--- a/themes.xlsx
+++ b/themes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E38A4ED9-E3B4-438F-86FF-6EB372A2093F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C77DD05A-4FEE-4A91-B42F-7E608A30EE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
   <sheets>
     <sheet name="themes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7939" uniqueCount="4005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8085" uniqueCount="4073">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -14961,6 +14961,258 @@
   </si>
   <si>
     <t>그 날</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1015,1130,1245,1400,1515,1640,1755,1910,2025,2140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>찰리이스케이프 2호점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl_esc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cl_esc2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀴즈카페2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀴즈카페2,퀴카2,quizcafe2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020,1150,1320,1450,1620,1750,1920,2050,2220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rec_hd</t>
+  </si>
+  <si>
+    <t>리얼 이스케이프 첼린지</t>
+  </si>
+  <si>
+    <t>rec_hd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rec_hd2</t>
+  </si>
+  <si>
+    <t>rec_hd3</t>
+  </si>
+  <si>
+    <t>rec_hd4</t>
+  </si>
+  <si>
+    <t>rec_hd5</t>
+  </si>
+  <si>
+    <t>셜록 : 교수의 비밀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로스트 : 그 남자의 경고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아르바이트 : 과학자의 속임수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐피드 : 러브 첼린지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미호 : 호령마을 미스테리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>큐피드 : 러브 첼린지,러브챌린지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미호 : 호령마을 미스터리,호령마을미스터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1120,1240,1400,1520,1640,1800,1920,2040,2200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1140,1300,1420,1540,1700,1820,1940,2100,2220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200,1320,1440,1600,1720,1840,2000,2120,2240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_hd2</t>
+  </si>
+  <si>
+    <t>미스터리 룸 이스케이프 홍대2호점</t>
+  </si>
+  <si>
+    <t>mre_hd2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_hd2_2</t>
+  </si>
+  <si>
+    <t>mre_hd2_4</t>
+  </si>
+  <si>
+    <t>쇼생크탈출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스파이게임1945</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THE BOOK - 소설책 속 남자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쏘우 - 0KG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_hd2_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THE BOOK - 소설책 속 남자,더북</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1인 25,000원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1120,1235,1350,1505,1620,1735,1850,2005,2120,2235</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bo_hd</t>
+  </si>
+  <si>
+    <t>브레이크아웃 이스케이프 홍대점</t>
+  </si>
+  <si>
+    <t>bo_hd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호커스1 - 마술사의 방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호커스2 - 비밀의 방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수상한 한의원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최후의 낙원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서리브럼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bo_hd2</t>
+  </si>
+  <si>
+    <t>bo_hd3</t>
+  </si>
+  <si>
+    <t>bo_hd4</t>
+  </si>
+  <si>
+    <t>bo_hd5</t>
+  </si>
+  <si>
+    <t>1320,1450,1610,1730,1850,2010,2130,2250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100,1230,1400,1530,1700,1820,1940,2100,2220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250,1420,1340,1700,1820,1940,2100,2220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030,1200,1330,1500,1630,1750,1910,1830,2150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_gn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인형괴담</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개인병원의 비밀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영혼의 편지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소서러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사라진 왕관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_gn1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미스터리 룸 이스케이프 강남점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mre_gn2</t>
+  </si>
+  <si>
+    <t>mre_gn3</t>
+  </si>
+  <si>
+    <t>mre_gn4</t>
+  </si>
+  <si>
+    <t>mre_gn5</t>
+  </si>
+  <si>
+    <t>1115,1230,1345,1500,1615,1730,1845,2000,2115,2230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,1115,1230,1345,1500,1615,1730,1845,2000,2115,2230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가오픈가 1인 29,000원 (3~5인)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15078,7 +15330,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15111,6 +15363,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15428,7 +15683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6A8B62-C038-47D4-9D17-9A5AC9BFE2AE}">
-  <dimension ref="A1:L993"/>
+  <dimension ref="A1:L1013"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
@@ -15437,7 +15692,7 @@
     <col min="4" max="4" width="28.125" customWidth="1"/>
     <col min="5" max="5" width="27.5" customWidth="1"/>
     <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.875" style="3" customWidth="1"/>
     <col min="8" max="8" width="41.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="7.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="45.75" style="1" customWidth="1"/>
@@ -15549,7 +15804,15 @@
       <c r="F4">
         <v>65</v>
       </c>
-      <c r="G4"/>
+      <c r="G4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>4005</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>4005</v>
+      </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
@@ -16705,10 +16968,10 @@
         <v>340</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>320</v>
+        <v>2570</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>236</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -16734,10 +16997,10 @@
         <v>340</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>318</v>
+        <v>2077</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>319</v>
+        <v>628</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -16763,10 +17026,10 @@
         <v>342</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>321</v>
+        <v>1292</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>313</v>
+        <v>546</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -31837,6 +32100,18 @@
       <c r="E565" s="1" t="s">
         <v>3840</v>
       </c>
+      <c r="F565">
+        <v>70</v>
+      </c>
+      <c r="G565" s="3" t="s">
+        <v>4072</v>
+      </c>
+      <c r="H565" s="1" t="s">
+        <v>4070</v>
+      </c>
+      <c r="J565" s="1" t="s">
+        <v>4071</v>
+      </c>
     </row>
     <row r="566" spans="1:10">
       <c r="A566" t="s">
@@ -44275,6 +44550,511 @@
       </c>
       <c r="J993" s="1" t="s">
         <v>320</v>
+      </c>
+    </row>
+    <row r="994" spans="1:10">
+      <c r="A994" s="1" t="s">
+        <v>4007</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>4006</v>
+      </c>
+      <c r="C994" s="1" t="s">
+        <v>4008</v>
+      </c>
+      <c r="D994" s="1" t="s">
+        <v>4009</v>
+      </c>
+      <c r="E994" s="1" t="s">
+        <v>4010</v>
+      </c>
+      <c r="F994">
+        <v>210</v>
+      </c>
+      <c r="G994" t="s">
+        <v>3846</v>
+      </c>
+      <c r="H994" s="1" t="s">
+        <v>3847</v>
+      </c>
+      <c r="J994" s="1" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="995" spans="1:10">
+      <c r="A995" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B995" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C995" t="s">
+        <v>4014</v>
+      </c>
+      <c r="D995" t="s">
+        <v>4019</v>
+      </c>
+      <c r="E995" t="s">
+        <v>4019</v>
+      </c>
+      <c r="F995">
+        <v>60</v>
+      </c>
+      <c r="G995" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H995" s="1" t="s">
+        <v>4026</v>
+      </c>
+      <c r="J995" s="1" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="996" spans="1:10">
+      <c r="A996" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B996" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C996" t="s">
+        <v>4015</v>
+      </c>
+      <c r="D996" t="s">
+        <v>4021</v>
+      </c>
+      <c r="E996" t="s">
+        <v>4021</v>
+      </c>
+      <c r="F996">
+        <v>60</v>
+      </c>
+      <c r="G996" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H996" s="1" t="s">
+        <v>4027</v>
+      </c>
+      <c r="J996" s="1" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="997" spans="1:10">
+      <c r="A997" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B997" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C997" t="s">
+        <v>4016</v>
+      </c>
+      <c r="D997" t="s">
+        <v>4022</v>
+      </c>
+      <c r="E997" t="s">
+        <v>4024</v>
+      </c>
+      <c r="F997">
+        <v>60</v>
+      </c>
+      <c r="G997" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H997" s="1" t="s">
+        <v>4027</v>
+      </c>
+      <c r="J997" s="1" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="998" spans="1:10">
+      <c r="A998" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B998" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C998" t="s">
+        <v>4017</v>
+      </c>
+      <c r="D998" t="s">
+        <v>4023</v>
+      </c>
+      <c r="E998" t="s">
+        <v>4025</v>
+      </c>
+      <c r="F998">
+        <v>60</v>
+      </c>
+      <c r="G998" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H998" s="1" t="s">
+        <v>4026</v>
+      </c>
+      <c r="J998" s="1" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="999" spans="1:10">
+      <c r="A999" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B999" s="12" t="s">
+        <v>4013</v>
+      </c>
+      <c r="C999" t="s">
+        <v>4018</v>
+      </c>
+      <c r="D999" t="s">
+        <v>4020</v>
+      </c>
+      <c r="E999" t="s">
+        <v>4020</v>
+      </c>
+      <c r="F999">
+        <v>60</v>
+      </c>
+      <c r="G999" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="H999" s="1" t="s">
+        <v>4028</v>
+      </c>
+      <c r="J999" s="1" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:10">
+      <c r="A1000" s="12" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B1000" s="12" t="s">
+        <v>4030</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>4031</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>4034</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>4034</v>
+      </c>
+      <c r="F1000">
+        <v>60</v>
+      </c>
+      <c r="G1000" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="H1000" s="1" t="s">
+        <v>4041</v>
+      </c>
+      <c r="J1000" s="1" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:10">
+      <c r="A1001" s="12" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B1001" s="12" t="s">
+        <v>4030</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>4032</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>4035</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>4035</v>
+      </c>
+      <c r="F1001">
+        <v>60</v>
+      </c>
+      <c r="G1001" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="H1001" s="1" t="s">
+        <v>4041</v>
+      </c>
+      <c r="J1001" s="1" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:10">
+      <c r="A1002" s="12" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B1002" s="12" t="s">
+        <v>4030</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>4038</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>4036</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>4039</v>
+      </c>
+      <c r="F1002">
+        <v>60</v>
+      </c>
+      <c r="G1002" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="H1002" s="1" t="s">
+        <v>4027</v>
+      </c>
+      <c r="J1002" s="1" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:10">
+      <c r="A1003" s="12" t="s">
+        <v>4029</v>
+      </c>
+      <c r="B1003" s="12" t="s">
+        <v>4030</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>4033</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>4037</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>4037</v>
+      </c>
+      <c r="F1003">
+        <v>60</v>
+      </c>
+      <c r="G1003" s="3" t="s">
+        <v>4040</v>
+      </c>
+      <c r="H1003" s="1" t="s">
+        <v>4027</v>
+      </c>
+      <c r="J1003" s="1" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:10">
+      <c r="A1004" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1004" s="12" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>4045</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>4045</v>
+      </c>
+      <c r="F1004">
+        <v>60</v>
+      </c>
+      <c r="G1004" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1004" s="1" t="s">
+        <v>4054</v>
+      </c>
+      <c r="J1004" s="1" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:10">
+      <c r="A1005" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1005" s="12" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>4050</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>4046</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>4046</v>
+      </c>
+      <c r="F1005">
+        <v>60</v>
+      </c>
+      <c r="G1005" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1005" s="1" t="s">
+        <v>4056</v>
+      </c>
+      <c r="J1005" s="1" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:10">
+      <c r="A1006" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1006" s="12" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>4051</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>4047</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>4047</v>
+      </c>
+      <c r="F1006">
+        <v>60</v>
+      </c>
+      <c r="G1006" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1006" s="1" t="s">
+        <v>4054</v>
+      </c>
+      <c r="J1006" s="1" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:10">
+      <c r="A1007" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1007" s="12" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>4052</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>4048</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>4048</v>
+      </c>
+      <c r="F1007">
+        <v>60</v>
+      </c>
+      <c r="G1007" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1007" s="1" t="s">
+        <v>4054</v>
+      </c>
+      <c r="J1007" s="1" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:10">
+      <c r="A1008" t="s">
+        <v>4042</v>
+      </c>
+      <c r="B1008" s="12" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>4053</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>4049</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>4049</v>
+      </c>
+      <c r="F1008">
+        <v>60</v>
+      </c>
+      <c r="G1008" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1008" s="1" t="s">
+        <v>4056</v>
+      </c>
+      <c r="J1008" s="1" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4">
+      <c r="A1009" s="12" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B1009" s="12" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C1009" s="12" t="s">
+        <v>4064</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4">
+      <c r="A1010" s="12" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B1010" s="12" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C1010" s="12" t="s">
+        <v>4066</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4">
+      <c r="A1011" s="12" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B1011" s="12" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C1011" s="12" t="s">
+        <v>4067</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4">
+      <c r="A1012" s="12" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B1012" s="12" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C1012" s="12" t="s">
+        <v>4068</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4">
+      <c r="A1013" s="12" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B1013" s="12" t="s">
+        <v>4065</v>
+      </c>
+      <c r="C1013" s="12" t="s">
+        <v>4069</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>4063</v>
       </c>
     </row>
   </sheetData>

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969432E7-96A1-4BF7-817B-57707BEDEC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C341B66-5595-4CB4-BD93-96AFB1E99F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10554" uniqueCount="5149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10593" uniqueCount="5167">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -19369,6 +19369,78 @@
   </si>
   <si>
     <t>1220,1340,1500,1620,1740,1900,2020,2140,2300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030,1145,1300,1415,1530,1645,1800,1915,2030,2145,2300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010,1125,1240,1355,1510,1625,1740,1855,2010,2125,2240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020,1135,1250,1405,1520,1635,1750,1905,2020,2135,2250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050,1205,1320,1435,1550,1705,1820,1935,2050,2205,2320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1040,1155,1310,1425,1540,1655,1810,1925,2040,2155,2310</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1055,1210,1325,1440,1555,1710,1825,1940,2055,2210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ptw_dj6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉봉쥬스 미스터리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ptw_dj7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평화고시원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0955,1110,1225,1340,1455,1610,1725,1840,1955,2110,2225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk_hv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLACK H[-]AVEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4F : 마지막 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1인 36,000원 (3~5인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1130,1330,1530,1730,1930,2130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030,1230,1430,1630,1830,2030,2230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bk_hv1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -19870,7 +19942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6A8B62-C038-47D4-9D17-9A5AC9BFE2AE}">
-  <dimension ref="A1:L1322"/>
+  <dimension ref="A1:L1325"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
@@ -39115,6 +39187,18 @@
       <c r="E662" s="11" t="s">
         <v>4156</v>
       </c>
+      <c r="F662">
+        <v>60</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H662" s="1" t="s">
+        <v>5149</v>
+      </c>
+      <c r="J662" s="1" t="s">
+        <v>5149</v>
+      </c>
     </row>
     <row r="663" spans="1:10">
       <c r="A663" s="11" t="s">
@@ -39132,6 +39216,18 @@
       <c r="E663" t="s">
         <v>4157</v>
       </c>
+      <c r="F663">
+        <v>60</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H663" s="1" t="s">
+        <v>5150</v>
+      </c>
+      <c r="J663" s="1" t="s">
+        <v>5150</v>
+      </c>
     </row>
     <row r="664" spans="1:10">
       <c r="A664" s="11" t="s">
@@ -39149,6 +39245,18 @@
       <c r="E664" t="s">
         <v>4158</v>
       </c>
+      <c r="F664">
+        <v>60</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H664" s="1" t="s">
+        <v>5151</v>
+      </c>
+      <c r="J664" s="1" t="s">
+        <v>5151</v>
+      </c>
     </row>
     <row r="665" spans="1:10">
       <c r="A665" s="11" t="s">
@@ -39166,6 +39274,18 @@
       <c r="E665" t="s">
         <v>4161</v>
       </c>
+      <c r="F665">
+        <v>60</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H665" s="1" t="s">
+        <v>5152</v>
+      </c>
+      <c r="J665" s="1" t="s">
+        <v>5152</v>
+      </c>
     </row>
     <row r="666" spans="1:10">
       <c r="A666" s="11" t="s">
@@ -39183,6 +39303,18 @@
       <c r="E666" t="s">
         <v>4162</v>
       </c>
+      <c r="F666">
+        <v>60</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H666" s="1" t="s">
+        <v>5153</v>
+      </c>
+      <c r="J666" s="1" t="s">
+        <v>5153</v>
+      </c>
     </row>
     <row r="667" spans="1:10">
       <c r="A667" s="11" t="s">
@@ -48275,6 +48407,12 @@
       <c r="G979" s="3" t="s">
         <v>339</v>
       </c>
+      <c r="H979" s="1" t="s">
+        <v>5154</v>
+      </c>
+      <c r="J979" s="1" t="s">
+        <v>5154</v>
+      </c>
     </row>
     <row r="980" spans="1:10">
       <c r="A980" t="s">
@@ -55412,19 +55550,19 @@
     </row>
     <row r="1226" spans="1:10">
       <c r="A1226" t="s">
-        <v>1989</v>
+        <v>2021</v>
       </c>
       <c r="B1226" t="s">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="C1226" t="s">
-        <v>1991</v>
+        <v>5155</v>
       </c>
       <c r="D1226" t="s">
-        <v>4686</v>
+        <v>5156</v>
       </c>
       <c r="E1226" t="s">
-        <v>1995</v>
+        <v>5156</v>
       </c>
       <c r="F1226">
         <v>60</v>
@@ -55433,39 +55571,33 @@
         <v>345</v>
       </c>
       <c r="H1226" s="1" t="s">
-        <v>1998</v>
+        <v>5159</v>
       </c>
       <c r="J1226" s="1" t="s">
-        <v>1998</v>
+        <v>5159</v>
       </c>
     </row>
     <row r="1227" spans="1:10">
       <c r="A1227" t="s">
-        <v>1989</v>
+        <v>2021</v>
       </c>
       <c r="B1227" t="s">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="C1227" t="s">
-        <v>2002</v>
+        <v>5157</v>
       </c>
       <c r="D1227" t="s">
-        <v>1992</v>
+        <v>5158</v>
       </c>
       <c r="E1227" t="s">
-        <v>1992</v>
+        <v>5158</v>
       </c>
       <c r="F1227">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1227" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H1227" s="1" t="s">
-        <v>1999</v>
-      </c>
-      <c r="J1227" s="1" t="s">
-        <v>1999</v>
+        <v>339</v>
       </c>
     </row>
     <row r="1228" spans="1:10">
@@ -55476,13 +55608,13 @@
         <v>1990</v>
       </c>
       <c r="C1228" t="s">
-        <v>2003</v>
+        <v>1991</v>
       </c>
       <c r="D1228" t="s">
-        <v>1993</v>
+        <v>4686</v>
       </c>
       <c r="E1228" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="F1228">
         <v>60</v>
@@ -55491,10 +55623,10 @@
         <v>345</v>
       </c>
       <c r="H1228" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="J1228" s="1" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1229" spans="1:10">
@@ -55505,13 +55637,13 @@
         <v>1990</v>
       </c>
       <c r="C1229" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D1229" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="E1229" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="F1229">
         <v>60</v>
@@ -55520,27 +55652,27 @@
         <v>345</v>
       </c>
       <c r="H1229" s="1" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="J1229" s="1" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1230" spans="1:10">
       <c r="A1230" t="s">
-        <v>1972</v>
+        <v>1989</v>
       </c>
       <c r="B1230" t="s">
-        <v>1973</v>
+        <v>1990</v>
       </c>
       <c r="C1230" t="s">
-        <v>1974</v>
+        <v>2003</v>
       </c>
       <c r="D1230" t="s">
-        <v>1977</v>
+        <v>1993</v>
       </c>
       <c r="E1230" t="s">
-        <v>1981</v>
+        <v>1996</v>
       </c>
       <c r="F1230">
         <v>60</v>
@@ -55549,27 +55681,27 @@
         <v>345</v>
       </c>
       <c r="H1230" s="1" t="s">
-        <v>1763</v>
+        <v>2000</v>
       </c>
       <c r="J1230" s="1" t="s">
-        <v>1763</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1231" spans="1:10">
       <c r="A1231" t="s">
-        <v>1972</v>
+        <v>1989</v>
       </c>
       <c r="B1231" t="s">
-        <v>1973</v>
+        <v>1990</v>
       </c>
       <c r="C1231" t="s">
-        <v>1985</v>
+        <v>2004</v>
       </c>
       <c r="D1231" t="s">
-        <v>1978</v>
+        <v>1994</v>
       </c>
       <c r="E1231" t="s">
-        <v>1982</v>
+        <v>1997</v>
       </c>
       <c r="F1231">
         <v>60</v>
@@ -55578,10 +55710,10 @@
         <v>345</v>
       </c>
       <c r="H1231" s="1" t="s">
-        <v>1961</v>
+        <v>2001</v>
       </c>
       <c r="J1231" s="1" t="s">
-        <v>1961</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1232" spans="1:10">
@@ -55592,25 +55724,25 @@
         <v>1973</v>
       </c>
       <c r="C1232" t="s">
-        <v>1986</v>
+        <v>1974</v>
       </c>
       <c r="D1232" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="E1232" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="F1232">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G1232" s="3" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="H1232" s="1" t="s">
-        <v>1980</v>
+        <v>1763</v>
       </c>
       <c r="J1232" s="1" t="s">
-        <v>1980</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1233" spans="1:10">
@@ -55621,13 +55753,13 @@
         <v>1973</v>
       </c>
       <c r="C1233" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="D1233" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="E1233" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F1233">
         <v>60</v>
@@ -55636,10 +55768,10 @@
         <v>345</v>
       </c>
       <c r="H1233" s="1" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="J1233" s="1" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1234" spans="1:10">
@@ -55650,42 +55782,42 @@
         <v>1973</v>
       </c>
       <c r="C1234" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="D1234" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="E1234" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="F1234">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G1234" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="H1234" s="1" t="s">
-        <v>1963</v>
+        <v>1980</v>
       </c>
       <c r="J1234" s="1" t="s">
-        <v>1963</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1235" spans="1:10">
       <c r="A1235" t="s">
-        <v>2005</v>
+        <v>1972</v>
       </c>
       <c r="B1235" t="s">
-        <v>2006</v>
+        <v>1973</v>
       </c>
       <c r="C1235" t="s">
-        <v>2007</v>
+        <v>1987</v>
       </c>
       <c r="D1235" t="s">
-        <v>2008</v>
+        <v>1976</v>
       </c>
       <c r="E1235" t="s">
-        <v>2008</v>
+        <v>1983</v>
       </c>
       <c r="F1235">
         <v>60</v>
@@ -55694,27 +55826,27 @@
         <v>345</v>
       </c>
       <c r="H1235" s="1" t="s">
-        <v>1750</v>
+        <v>1966</v>
       </c>
       <c r="J1235" s="1" t="s">
-        <v>1750</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1236" spans="1:10">
       <c r="A1236" t="s">
-        <v>2005</v>
+        <v>1972</v>
       </c>
       <c r="B1236" t="s">
-        <v>2006</v>
+        <v>1973</v>
       </c>
       <c r="C1236" t="s">
-        <v>2016</v>
+        <v>1988</v>
       </c>
       <c r="D1236" t="s">
-        <v>2009</v>
+        <v>1975</v>
       </c>
       <c r="E1236" t="s">
-        <v>2009</v>
+        <v>1984</v>
       </c>
       <c r="F1236">
         <v>60</v>
@@ -55723,10 +55855,10 @@
         <v>345</v>
       </c>
       <c r="H1236" s="1" t="s">
-        <v>2011</v>
+        <v>1963</v>
       </c>
       <c r="J1236" s="1" t="s">
-        <v>2011</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1237" spans="1:10">
@@ -55737,13 +55869,13 @@
         <v>2006</v>
       </c>
       <c r="C1237" t="s">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="D1237" t="s">
-        <v>2766</v>
+        <v>2008</v>
       </c>
       <c r="E1237" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="F1237">
         <v>60</v>
@@ -55752,10 +55884,10 @@
         <v>345</v>
       </c>
       <c r="H1237" s="1" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
       <c r="J1237" s="1" t="s">
-        <v>1720</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1238" spans="1:10">
@@ -55766,13 +55898,13 @@
         <v>2006</v>
       </c>
       <c r="C1238" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D1238" t="s">
-        <v>2250</v>
+        <v>2009</v>
       </c>
       <c r="E1238" t="s">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F1238">
         <v>60</v>
@@ -55781,10 +55913,10 @@
         <v>345</v>
       </c>
       <c r="H1238" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="J1238" s="1" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1239" spans="1:10">
@@ -55795,13 +55927,13 @@
         <v>2006</v>
       </c>
       <c r="C1239" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D1239" t="s">
-        <v>2756</v>
+        <v>2766</v>
       </c>
       <c r="E1239" t="s">
-        <v>772</v>
+        <v>2010</v>
       </c>
       <c r="F1239">
         <v>60</v>
@@ -55810,10 +55942,10 @@
         <v>345</v>
       </c>
       <c r="H1239" s="1" t="s">
-        <v>2013</v>
+        <v>1720</v>
       </c>
       <c r="J1239" s="1" t="s">
-        <v>2013</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1240" spans="1:10">
@@ -55824,13 +55956,13 @@
         <v>2006</v>
       </c>
       <c r="C1240" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D1240" t="s">
-        <v>2770</v>
+        <v>2250</v>
       </c>
       <c r="E1240" t="s">
-        <v>771</v>
+        <v>2015</v>
       </c>
       <c r="F1240">
         <v>60</v>
@@ -55839,56 +55971,56 @@
         <v>345</v>
       </c>
       <c r="H1240" s="1" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="J1240" s="1" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1241" spans="1:10">
-      <c r="A1241" s="8" t="s">
-        <v>4922</v>
-      </c>
-      <c r="B1241" s="9" t="s">
-        <v>4923</v>
-      </c>
-      <c r="C1241" s="8" t="s">
-        <v>4924</v>
-      </c>
-      <c r="D1241" s="9" t="s">
-        <v>4925</v>
-      </c>
-      <c r="E1241" s="9" t="s">
-        <v>4925</v>
+      <c r="A1241" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>2756</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>772</v>
       </c>
       <c r="F1241">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="G1241" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="H1241" s="1" t="s">
-        <v>4926</v>
+        <v>2013</v>
       </c>
       <c r="J1241" s="1" t="s">
-        <v>4926</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="1242" spans="1:10">
       <c r="A1242" t="s">
-        <v>1897</v>
+        <v>2005</v>
       </c>
       <c r="B1242" t="s">
-        <v>1899</v>
+        <v>2006</v>
       </c>
       <c r="C1242" t="s">
-        <v>1898</v>
+        <v>2020</v>
       </c>
       <c r="D1242" t="s">
-        <v>2096</v>
+        <v>2770</v>
       </c>
       <c r="E1242" t="s">
-        <v>1900</v>
+        <v>771</v>
       </c>
       <c r="F1242">
         <v>60</v>
@@ -55897,39 +56029,39 @@
         <v>345</v>
       </c>
       <c r="H1242" s="1" t="s">
-        <v>1910</v>
+        <v>2014</v>
       </c>
       <c r="J1242" s="1" t="s">
-        <v>987</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1243" spans="1:10">
-      <c r="A1243" t="s">
-        <v>1897</v>
-      </c>
-      <c r="B1243" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C1243" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D1243" t="s">
-        <v>1901</v>
-      </c>
-      <c r="E1243" t="s">
-        <v>1901</v>
+      <c r="A1243" s="8" t="s">
+        <v>4922</v>
+      </c>
+      <c r="B1243" s="9" t="s">
+        <v>4923</v>
+      </c>
+      <c r="C1243" s="8" t="s">
+        <v>4924</v>
+      </c>
+      <c r="D1243" s="9" t="s">
+        <v>4925</v>
+      </c>
+      <c r="E1243" s="9" t="s">
+        <v>4925</v>
       </c>
       <c r="F1243">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="G1243" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="H1243" s="1" t="s">
-        <v>1911</v>
+        <v>4926</v>
       </c>
       <c r="J1243" s="1" t="s">
-        <v>1906</v>
+        <v>4926</v>
       </c>
     </row>
     <row r="1244" spans="1:10">
@@ -55940,25 +56072,25 @@
         <v>1899</v>
       </c>
       <c r="C1244" t="s">
-        <v>1917</v>
+        <v>1898</v>
       </c>
       <c r="D1244" t="s">
-        <v>1902</v>
+        <v>2096</v>
       </c>
       <c r="E1244" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F1244">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G1244" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H1244" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="J1244" s="1" t="s">
-        <v>1907</v>
+        <v>987</v>
       </c>
     </row>
     <row r="1245" spans="1:10">
@@ -55969,25 +56101,25 @@
         <v>1899</v>
       </c>
       <c r="C1245" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="D1245" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="E1245" t="s">
-        <v>1915</v>
+        <v>1901</v>
       </c>
       <c r="F1245">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G1245" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1245" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="J1245" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1246" spans="1:10">
@@ -55998,25 +56130,25 @@
         <v>1899</v>
       </c>
       <c r="C1246" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="D1246" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="E1246" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="F1246">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G1246" s="3" t="s">
-        <v>1905</v>
+        <v>340</v>
       </c>
       <c r="H1246" s="1" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="J1246" s="1" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1247" spans="1:10">
@@ -56027,83 +56159,83 @@
         <v>1899</v>
       </c>
       <c r="C1247" t="s">
-        <v>2632</v>
+        <v>1918</v>
       </c>
       <c r="D1247" t="s">
-        <v>2633</v>
+        <v>1903</v>
       </c>
       <c r="E1247" t="s">
-        <v>2633</v>
+        <v>1915</v>
       </c>
       <c r="F1247">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G1247" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1247" s="1" t="s">
-        <v>2634</v>
+        <v>1913</v>
       </c>
       <c r="J1247" s="1" t="s">
-        <v>2636</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1248" spans="1:10">
       <c r="A1248" t="s">
-        <v>2039</v>
+        <v>1897</v>
       </c>
       <c r="B1248" t="s">
-        <v>2040</v>
+        <v>1899</v>
       </c>
       <c r="C1248" t="s">
-        <v>2041</v>
+        <v>1919</v>
       </c>
       <c r="D1248" t="s">
-        <v>2042</v>
+        <v>1904</v>
       </c>
       <c r="E1248" t="s">
-        <v>2054</v>
+        <v>1904</v>
       </c>
       <c r="F1248">
         <v>60</v>
       </c>
       <c r="G1248" s="3" t="s">
-        <v>345</v>
+        <v>1905</v>
       </c>
       <c r="H1248" s="1" t="s">
-        <v>2050</v>
+        <v>1914</v>
       </c>
       <c r="J1248" s="1" t="s">
-        <v>2046</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1249" spans="1:10">
       <c r="A1249" t="s">
-        <v>2039</v>
+        <v>1897</v>
       </c>
       <c r="B1249" t="s">
-        <v>2040</v>
+        <v>1899</v>
       </c>
       <c r="C1249" t="s">
-        <v>2056</v>
+        <v>2632</v>
       </c>
       <c r="D1249" t="s">
-        <v>2043</v>
+        <v>2633</v>
       </c>
       <c r="E1249" t="s">
-        <v>2055</v>
+        <v>2633</v>
       </c>
       <c r="F1249">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1249" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1249" s="1" t="s">
-        <v>2051</v>
+        <v>2634</v>
       </c>
       <c r="J1249" s="1" t="s">
-        <v>2047</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="1250" spans="1:10">
@@ -56114,13 +56246,13 @@
         <v>2040</v>
       </c>
       <c r="C1250" t="s">
-        <v>2057</v>
+        <v>2041</v>
       </c>
       <c r="D1250" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="E1250" t="s">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="F1250">
         <v>60</v>
@@ -56129,10 +56261,10 @@
         <v>345</v>
       </c>
       <c r="H1250" s="1" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="J1250" s="1" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1251" spans="1:10">
@@ -56143,13 +56275,13 @@
         <v>2040</v>
       </c>
       <c r="C1251" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="D1251" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="E1251" t="s">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="F1251">
         <v>60</v>
@@ -56158,68 +56290,68 @@
         <v>345</v>
       </c>
       <c r="H1251" s="1" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="J1251" s="1" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1252" spans="1:10">
       <c r="A1252" t="s">
-        <v>2075</v>
+        <v>2039</v>
       </c>
       <c r="B1252" t="s">
-        <v>3177</v>
+        <v>2040</v>
       </c>
       <c r="C1252" t="s">
-        <v>2076</v>
+        <v>2057</v>
       </c>
       <c r="D1252" t="s">
-        <v>2069</v>
+        <v>2044</v>
       </c>
       <c r="E1252" t="s">
-        <v>2069</v>
+        <v>2044</v>
       </c>
       <c r="F1252">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G1252" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H1252" s="1" t="s">
-        <v>2073</v>
+        <v>2052</v>
       </c>
       <c r="J1252" s="1" t="s">
-        <v>469</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1253" spans="1:10">
       <c r="A1253" t="s">
-        <v>2075</v>
+        <v>2039</v>
       </c>
       <c r="B1253" t="s">
-        <v>3177</v>
+        <v>2040</v>
       </c>
       <c r="C1253" t="s">
-        <v>2077</v>
+        <v>2058</v>
       </c>
       <c r="D1253" t="s">
-        <v>2757</v>
+        <v>2045</v>
       </c>
       <c r="E1253" t="s">
-        <v>772</v>
+        <v>2045</v>
       </c>
       <c r="F1253">
         <v>60</v>
       </c>
       <c r="G1253" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H1253" s="1" t="s">
-        <v>319</v>
+        <v>2053</v>
       </c>
       <c r="J1253" s="1" t="s">
-        <v>832</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1254" spans="1:10">
@@ -56230,25 +56362,25 @@
         <v>3177</v>
       </c>
       <c r="C1254" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="D1254" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="E1254" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F1254">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G1254" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H1254" s="1" t="s">
-        <v>316</v>
+        <v>2073</v>
       </c>
       <c r="J1254" s="1" t="s">
-        <v>378</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1255" spans="1:10">
@@ -56259,83 +56391,83 @@
         <v>3177</v>
       </c>
       <c r="C1255" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="D1255" t="s">
-        <v>2071</v>
+        <v>2757</v>
       </c>
       <c r="E1255" t="s">
-        <v>2072</v>
+        <v>772</v>
       </c>
       <c r="F1255">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G1255" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H1255" s="1" t="s">
-        <v>2074</v>
+        <v>319</v>
       </c>
       <c r="J1255" s="1" t="s">
-        <v>468</v>
+        <v>832</v>
       </c>
     </row>
     <row r="1256" spans="1:10">
       <c r="A1256" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="B1256" t="s">
-        <v>2081</v>
+        <v>3177</v>
       </c>
       <c r="C1256" t="s">
-        <v>2086</v>
+        <v>2078</v>
       </c>
       <c r="D1256" t="s">
-        <v>2589</v>
+        <v>2070</v>
       </c>
       <c r="E1256" t="s">
-        <v>2590</v>
+        <v>2070</v>
       </c>
       <c r="F1256">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G1256" s="3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="H1256" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J1256" s="1" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
     </row>
     <row r="1257" spans="1:10">
       <c r="A1257" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="B1257" t="s">
-        <v>2081</v>
+        <v>3177</v>
       </c>
       <c r="C1257" t="s">
-        <v>2087</v>
+        <v>2079</v>
       </c>
       <c r="D1257" t="s">
-        <v>2082</v>
+        <v>2071</v>
       </c>
       <c r="E1257" t="s">
-        <v>2082</v>
+        <v>2072</v>
       </c>
       <c r="F1257">
         <v>70</v>
       </c>
       <c r="G1257" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H1257" s="1" t="s">
         <v>2074</v>
       </c>
       <c r="J1257" s="1" t="s">
-        <v>2085</v>
+        <v>468</v>
       </c>
     </row>
     <row r="1258" spans="1:10">
@@ -56346,83 +56478,83 @@
         <v>2081</v>
       </c>
       <c r="C1258" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="D1258" t="s">
-        <v>2083</v>
+        <v>2589</v>
       </c>
       <c r="E1258" t="s">
-        <v>2084</v>
+        <v>2590</v>
       </c>
       <c r="F1258">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G1258" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="H1258" s="1" t="s">
-        <v>2073</v>
+        <v>318</v>
       </c>
       <c r="J1258" s="1" t="s">
-        <v>247</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1259" spans="1:10">
       <c r="A1259" t="s">
-        <v>2158</v>
+        <v>2080</v>
       </c>
       <c r="B1259" t="s">
-        <v>2159</v>
+        <v>2081</v>
       </c>
       <c r="C1259" t="s">
-        <v>2172</v>
+        <v>2087</v>
       </c>
       <c r="D1259" t="s">
-        <v>2160</v>
+        <v>2082</v>
       </c>
       <c r="E1259" t="s">
-        <v>2160</v>
+        <v>2082</v>
       </c>
       <c r="F1259">
         <v>70</v>
       </c>
       <c r="G1259" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H1259" s="1" t="s">
-        <v>570</v>
+        <v>2074</v>
       </c>
       <c r="J1259" s="1" t="s">
-        <v>467</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1260" spans="1:10">
       <c r="A1260" t="s">
-        <v>2158</v>
+        <v>2080</v>
       </c>
       <c r="B1260" t="s">
-        <v>2159</v>
+        <v>2081</v>
       </c>
       <c r="C1260" t="s">
-        <v>2173</v>
+        <v>2088</v>
       </c>
       <c r="D1260" t="s">
-        <v>2161</v>
+        <v>2083</v>
       </c>
       <c r="E1260" t="s">
-        <v>2161</v>
+        <v>2084</v>
       </c>
       <c r="F1260">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G1260" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H1260" s="1" t="s">
-        <v>1908</v>
+        <v>2073</v>
       </c>
       <c r="J1260" s="1" t="s">
-        <v>849</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1261" spans="1:10">
@@ -56433,25 +56565,25 @@
         <v>2159</v>
       </c>
       <c r="C1261" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="D1261" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="E1261" t="s">
-        <v>2167</v>
+        <v>2160</v>
       </c>
       <c r="F1261">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1261" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1261" s="1" t="s">
-        <v>1340</v>
+        <v>570</v>
       </c>
       <c r="J1261" s="1" t="s">
-        <v>850</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1262" spans="1:10">
@@ -56462,13 +56594,13 @@
         <v>2159</v>
       </c>
       <c r="C1262" t="s">
-        <v>2591</v>
+        <v>2173</v>
       </c>
       <c r="D1262" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="E1262" t="s">
-        <v>2168</v>
+        <v>2161</v>
       </c>
       <c r="F1262">
         <v>60</v>
@@ -56477,10 +56609,10 @@
         <v>345</v>
       </c>
       <c r="H1262" s="1" t="s">
-        <v>840</v>
+        <v>1908</v>
       </c>
       <c r="J1262" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="1263" spans="1:10">
@@ -56491,13 +56623,13 @@
         <v>2159</v>
       </c>
       <c r="C1263" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="D1263" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="E1263" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="F1263">
         <v>60</v>
@@ -56506,10 +56638,10 @@
         <v>345</v>
       </c>
       <c r="H1263" s="1" t="s">
-        <v>842</v>
+        <v>1340</v>
       </c>
       <c r="J1263" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="1264" spans="1:10">
@@ -56520,13 +56652,13 @@
         <v>2159</v>
       </c>
       <c r="C1264" t="s">
-        <v>2176</v>
+        <v>2591</v>
       </c>
       <c r="D1264" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="E1264" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="F1264">
         <v>60</v>
@@ -56535,27 +56667,27 @@
         <v>345</v>
       </c>
       <c r="H1264" s="1" t="s">
-        <v>2171</v>
+        <v>840</v>
       </c>
       <c r="J1264" s="1" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
     </row>
     <row r="1265" spans="1:10">
       <c r="A1265" t="s">
-        <v>2218</v>
+        <v>2158</v>
       </c>
       <c r="B1265" t="s">
-        <v>2219</v>
+        <v>2159</v>
       </c>
       <c r="C1265" t="s">
-        <v>2220</v>
+        <v>2175</v>
       </c>
       <c r="D1265" t="s">
-        <v>2221</v>
+        <v>2165</v>
       </c>
       <c r="E1265" t="s">
-        <v>2227</v>
+        <v>2169</v>
       </c>
       <c r="F1265">
         <v>60</v>
@@ -56564,27 +56696,27 @@
         <v>345</v>
       </c>
       <c r="H1265" s="1" t="s">
-        <v>256</v>
+        <v>842</v>
       </c>
       <c r="J1265" s="1" t="s">
-        <v>256</v>
+        <v>851</v>
       </c>
     </row>
     <row r="1266" spans="1:10">
       <c r="A1266" t="s">
-        <v>2218</v>
+        <v>2158</v>
       </c>
       <c r="B1266" t="s">
-        <v>2219</v>
+        <v>2159</v>
       </c>
       <c r="C1266" t="s">
-        <v>2230</v>
+        <v>2176</v>
       </c>
       <c r="D1266" t="s">
-        <v>3679</v>
+        <v>2166</v>
       </c>
       <c r="E1266" t="s">
-        <v>2228</v>
+        <v>2170</v>
       </c>
       <c r="F1266">
         <v>60</v>
@@ -56593,10 +56725,10 @@
         <v>345</v>
       </c>
       <c r="H1266" s="1" t="s">
-        <v>2208</v>
+        <v>2171</v>
       </c>
       <c r="J1266" s="1" t="s">
-        <v>2208</v>
+        <v>853</v>
       </c>
     </row>
     <row r="1267" spans="1:10">
@@ -56607,13 +56739,13 @@
         <v>2219</v>
       </c>
       <c r="C1267" t="s">
-        <v>2231</v>
+        <v>2220</v>
       </c>
       <c r="D1267" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="E1267" t="s">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="F1267">
         <v>60</v>
@@ -56622,10 +56754,10 @@
         <v>345</v>
       </c>
       <c r="H1267" s="1" t="s">
-        <v>2206</v>
+        <v>256</v>
       </c>
       <c r="J1267" s="1" t="s">
-        <v>2206</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1268" spans="1:10">
@@ -56636,13 +56768,13 @@
         <v>2219</v>
       </c>
       <c r="C1268" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="D1268" t="s">
-        <v>2224</v>
+        <v>3679</v>
       </c>
       <c r="E1268" t="s">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="F1268">
         <v>60</v>
@@ -56651,10 +56783,10 @@
         <v>345</v>
       </c>
       <c r="H1268" s="1" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="J1268" s="1" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1269" spans="1:10">
@@ -56665,13 +56797,13 @@
         <v>2219</v>
       </c>
       <c r="C1269" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="D1269" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="E1269" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="F1269">
         <v>60</v>
@@ -56680,10 +56812,10 @@
         <v>345</v>
       </c>
       <c r="H1269" s="1" t="s">
-        <v>545</v>
+        <v>2206</v>
       </c>
       <c r="J1269" s="1" t="s">
-        <v>545</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1270" spans="1:10">
@@ -56694,13 +56826,13 @@
         <v>2219</v>
       </c>
       <c r="C1270" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="D1270" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="E1270" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
       <c r="F1270">
         <v>60</v>
@@ -56709,68 +56841,68 @@
         <v>345</v>
       </c>
       <c r="H1270" s="1" t="s">
-        <v>309</v>
+        <v>2207</v>
       </c>
       <c r="J1270" s="1" t="s">
-        <v>309</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="1271" spans="1:10">
       <c r="A1271" t="s">
-        <v>2177</v>
+        <v>2218</v>
       </c>
       <c r="B1271" t="s">
-        <v>2178</v>
+        <v>2219</v>
       </c>
       <c r="C1271" t="s">
-        <v>2179</v>
+        <v>2233</v>
       </c>
       <c r="D1271" t="s">
-        <v>2180</v>
+        <v>2225</v>
       </c>
       <c r="E1271" t="s">
-        <v>2180</v>
+        <v>2225</v>
       </c>
       <c r="F1271">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G1271" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H1271" s="1" t="s">
-        <v>206</v>
+        <v>545</v>
       </c>
       <c r="J1271" s="1" t="s">
-        <v>206</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1272" spans="1:10">
       <c r="A1272" t="s">
-        <v>2177</v>
+        <v>2218</v>
       </c>
       <c r="B1272" t="s">
-        <v>2178</v>
+        <v>2219</v>
       </c>
       <c r="C1272" t="s">
-        <v>2189</v>
+        <v>2234</v>
       </c>
       <c r="D1272" t="s">
-        <v>2181</v>
+        <v>2226</v>
       </c>
       <c r="E1272" t="s">
-        <v>2181</v>
+        <v>2229</v>
       </c>
       <c r="F1272">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G1272" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H1272" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="J1272" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1273" spans="1:10">
@@ -56781,13 +56913,13 @@
         <v>2178</v>
       </c>
       <c r="C1273" t="s">
-        <v>2190</v>
+        <v>2179</v>
       </c>
       <c r="D1273" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="E1273" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="F1273">
         <v>70</v>
@@ -56796,10 +56928,10 @@
         <v>340</v>
       </c>
       <c r="H1273" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J1273" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1274" spans="1:10">
@@ -56810,13 +56942,13 @@
         <v>2178</v>
       </c>
       <c r="C1274" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="D1274" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="E1274" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="F1274">
         <v>70</v>
@@ -56825,10 +56957,10 @@
         <v>340</v>
       </c>
       <c r="H1274" s="1" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="J1274" s="1" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1275" spans="1:10">
@@ -56839,25 +56971,25 @@
         <v>2178</v>
       </c>
       <c r="C1275" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="D1275" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="E1275" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="F1275">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1275" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1275" s="1" t="s">
-        <v>2187</v>
+        <v>203</v>
       </c>
       <c r="J1275" s="1" t="s">
-        <v>2187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1276" spans="1:10">
@@ -56868,83 +57000,83 @@
         <v>2178</v>
       </c>
       <c r="C1276" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="D1276" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="E1276" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="F1276">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1276" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1276" s="1" t="s">
-        <v>2188</v>
+        <v>204</v>
       </c>
       <c r="J1276" s="1" t="s">
-        <v>2188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1277" spans="1:10">
       <c r="A1277" t="s">
-        <v>2089</v>
+        <v>2177</v>
       </c>
       <c r="B1277" t="s">
-        <v>2090</v>
+        <v>2178</v>
       </c>
       <c r="C1277" t="s">
-        <v>2098</v>
+        <v>2192</v>
       </c>
       <c r="D1277" t="s">
-        <v>2091</v>
+        <v>2184</v>
       </c>
       <c r="E1277" t="s">
-        <v>2104</v>
+        <v>2184</v>
       </c>
       <c r="F1277">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G1277" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H1277" s="1" t="s">
-        <v>378</v>
+        <v>2187</v>
       </c>
       <c r="J1277" s="1" t="s">
-        <v>234</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="1278" spans="1:10">
       <c r="A1278" t="s">
-        <v>2089</v>
+        <v>2177</v>
       </c>
       <c r="B1278" t="s">
-        <v>2090</v>
+        <v>2178</v>
       </c>
       <c r="C1278" t="s">
-        <v>2099</v>
+        <v>2193</v>
       </c>
       <c r="D1278" t="s">
-        <v>2092</v>
+        <v>2185</v>
       </c>
       <c r="E1278" t="s">
-        <v>2105</v>
+        <v>2185</v>
       </c>
       <c r="F1278">
         <v>60</v>
       </c>
       <c r="G1278" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H1278" s="1" t="s">
-        <v>983</v>
+        <v>2188</v>
       </c>
       <c r="J1278" s="1" t="s">
-        <v>2106</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="1279" spans="1:10">
@@ -56955,25 +57087,25 @@
         <v>2090</v>
       </c>
       <c r="C1279" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="D1279" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="E1279" t="s">
-        <v>2093</v>
+        <v>2104</v>
       </c>
       <c r="F1279">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G1279" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="H1279" s="1" t="s">
-        <v>2109</v>
+        <v>378</v>
       </c>
       <c r="J1279" s="1" t="s">
-        <v>2107</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1280" spans="1:10">
@@ -56984,25 +57116,25 @@
         <v>2090</v>
       </c>
       <c r="C1280" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="D1280" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="E1280" t="s">
-        <v>1900</v>
+        <v>2105</v>
       </c>
       <c r="F1280">
         <v>60</v>
       </c>
       <c r="G1280" s="3" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H1280" s="1" t="s">
-        <v>850</v>
+        <v>983</v>
       </c>
       <c r="J1280" s="1" t="s">
-        <v>545</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1281" spans="1:10">
@@ -57013,25 +57145,25 @@
         <v>2090</v>
       </c>
       <c r="C1281" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="D1281" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="E1281" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="F1281">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G1281" s="3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="H1281" s="1" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="J1281" s="1" t="s">
-        <v>626</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1282" spans="1:10">
@@ -57042,13 +57174,13 @@
         <v>2090</v>
       </c>
       <c r="C1282" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="D1282" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="E1282" t="s">
-        <v>2095</v>
+        <v>1900</v>
       </c>
       <c r="F1282">
         <v>60</v>
@@ -57057,56 +57189,56 @@
         <v>345</v>
       </c>
       <c r="H1282" s="1" t="s">
-        <v>2111</v>
+        <v>850</v>
       </c>
       <c r="J1282" s="1" t="s">
-        <v>2108</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1283" spans="1:10">
       <c r="A1283" t="s">
-        <v>2209</v>
+        <v>2089</v>
       </c>
       <c r="B1283" t="s">
-        <v>2210</v>
+        <v>2090</v>
       </c>
       <c r="C1283" t="s">
-        <v>2211</v>
+        <v>2102</v>
       </c>
       <c r="D1283" t="s">
-        <v>2212</v>
+        <v>2094</v>
       </c>
       <c r="E1283" t="s">
-        <v>2212</v>
+        <v>2094</v>
       </c>
       <c r="F1283">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1283" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="H1283" s="1" t="s">
-        <v>896</v>
+        <v>2110</v>
       </c>
       <c r="J1283" s="1" t="s">
-        <v>896</v>
+        <v>626</v>
       </c>
     </row>
     <row r="1284" spans="1:10">
       <c r="A1284" t="s">
-        <v>2209</v>
+        <v>2089</v>
       </c>
       <c r="B1284" t="s">
-        <v>2210</v>
+        <v>2090</v>
       </c>
       <c r="C1284" t="s">
-        <v>2216</v>
+        <v>2103</v>
       </c>
       <c r="D1284" t="s">
-        <v>2213</v>
+        <v>2095</v>
       </c>
       <c r="E1284" t="s">
-        <v>2213</v>
+        <v>2095</v>
       </c>
       <c r="F1284">
         <v>60</v>
@@ -57115,10 +57247,10 @@
         <v>345</v>
       </c>
       <c r="H1284" s="1" t="s">
-        <v>136</v>
+        <v>2111</v>
       </c>
       <c r="J1284" s="1" t="s">
-        <v>136</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1285" spans="1:10">
@@ -57129,13 +57261,13 @@
         <v>2210</v>
       </c>
       <c r="C1285" t="s">
-        <v>2217</v>
+        <v>2211</v>
       </c>
       <c r="D1285" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="E1285" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="F1285">
         <v>60</v>
@@ -57144,68 +57276,68 @@
         <v>345</v>
       </c>
       <c r="H1285" s="1" t="s">
-        <v>1773</v>
+        <v>896</v>
       </c>
       <c r="J1285" s="1" t="s">
-        <v>1773</v>
+        <v>896</v>
       </c>
     </row>
     <row r="1286" spans="1:10">
       <c r="A1286" t="s">
-        <v>379</v>
+        <v>2209</v>
       </c>
       <c r="B1286" t="s">
-        <v>27</v>
+        <v>2210</v>
       </c>
       <c r="C1286" t="s">
-        <v>380</v>
+        <v>2216</v>
       </c>
       <c r="D1286" t="s">
-        <v>3300</v>
+        <v>2213</v>
       </c>
       <c r="E1286" t="s">
-        <v>3301</v>
+        <v>2213</v>
       </c>
       <c r="F1286">
         <v>60</v>
       </c>
       <c r="G1286" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H1286" s="1" t="s">
-        <v>611</v>
+        <v>136</v>
       </c>
       <c r="J1286" s="1" t="s">
-        <v>610</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1287" spans="1:10">
       <c r="A1287" t="s">
-        <v>379</v>
+        <v>2209</v>
       </c>
       <c r="B1287" t="s">
-        <v>27</v>
+        <v>2210</v>
       </c>
       <c r="C1287" t="s">
-        <v>381</v>
+        <v>2217</v>
       </c>
       <c r="D1287" t="s">
-        <v>607</v>
+        <v>2214</v>
       </c>
       <c r="E1287" t="s">
-        <v>608</v>
+        <v>2215</v>
       </c>
       <c r="F1287">
         <v>60</v>
       </c>
       <c r="G1287" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="H1287" s="1" t="s">
-        <v>613</v>
+        <v>1773</v>
       </c>
       <c r="J1287" s="1" t="s">
-        <v>612</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1288" spans="1:10">
@@ -57216,25 +57348,25 @@
         <v>27</v>
       </c>
       <c r="C1288" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D1288" t="s">
-        <v>384</v>
+        <v>3300</v>
       </c>
       <c r="E1288" t="s">
-        <v>609</v>
+        <v>3301</v>
       </c>
       <c r="F1288">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G1288" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H1288" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="J1288" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="1289" spans="1:10">
@@ -57245,13 +57377,13 @@
         <v>27</v>
       </c>
       <c r="C1289" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D1289" t="s">
-        <v>385</v>
+        <v>607</v>
       </c>
       <c r="E1289" t="s">
-        <v>385</v>
+        <v>608</v>
       </c>
       <c r="F1289">
         <v>60</v>
@@ -57260,172 +57392,172 @@
         <v>340</v>
       </c>
       <c r="H1289" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="J1289" s="1" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="1290" spans="1:10">
       <c r="A1290" t="s">
-        <v>2498</v>
+        <v>379</v>
       </c>
       <c r="B1290" t="s">
-        <v>2509</v>
+        <v>27</v>
       </c>
       <c r="C1290" t="s">
-        <v>2506</v>
+        <v>382</v>
       </c>
       <c r="D1290" t="s">
-        <v>2499</v>
+        <v>384</v>
       </c>
       <c r="E1290" t="s">
-        <v>2500</v>
+        <v>609</v>
       </c>
       <c r="F1290">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G1290" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H1290" s="1" t="s">
-        <v>2501</v>
+        <v>615</v>
       </c>
       <c r="J1290" s="1" t="s">
-        <v>2502</v>
+        <v>614</v>
       </c>
     </row>
     <row r="1291" spans="1:10">
       <c r="A1291" t="s">
-        <v>2498</v>
+        <v>379</v>
       </c>
       <c r="B1291" t="s">
-        <v>2509</v>
+        <v>27</v>
       </c>
       <c r="C1291" t="s">
-        <v>2507</v>
+        <v>383</v>
       </c>
       <c r="D1291" t="s">
-        <v>2504</v>
+        <v>385</v>
       </c>
       <c r="E1291" t="s">
-        <v>2505</v>
+        <v>385</v>
       </c>
       <c r="F1291">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G1291" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="H1291" s="1" t="s">
-        <v>2503</v>
+        <v>616</v>
       </c>
       <c r="J1291" s="1" t="s">
-        <v>1534</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1292" spans="1:10">
       <c r="A1292" t="s">
-        <v>2508</v>
+        <v>2498</v>
       </c>
       <c r="B1292" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C1292" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1292" t="s">
-        <v>2512</v>
+        <v>2499</v>
       </c>
       <c r="E1292" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="F1292">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G1292" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H1292" s="1" t="s">
-        <v>2518</v>
+        <v>2501</v>
       </c>
       <c r="J1292" s="1" t="s">
-        <v>914</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="1293" spans="1:10">
       <c r="A1293" t="s">
-        <v>2508</v>
+        <v>2498</v>
       </c>
       <c r="B1293" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C1293" t="s">
-        <v>2517</v>
+        <v>2507</v>
       </c>
       <c r="D1293" t="s">
-        <v>2514</v>
+        <v>2504</v>
       </c>
       <c r="E1293" t="s">
-        <v>2515</v>
+        <v>2505</v>
       </c>
       <c r="F1293">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G1293" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="H1293" s="1" t="s">
-        <v>2519</v>
+        <v>2503</v>
       </c>
       <c r="J1293" s="1" t="s">
-        <v>2516</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1294" spans="1:10">
       <c r="A1294" t="s">
-        <v>2569</v>
+        <v>2508</v>
       </c>
       <c r="B1294" t="s">
-        <v>2570</v>
+        <v>2510</v>
       </c>
       <c r="C1294" t="s">
-        <v>2571</v>
+        <v>2511</v>
       </c>
       <c r="D1294" t="s">
-        <v>2572</v>
+        <v>2512</v>
       </c>
       <c r="E1294" t="s">
-        <v>2573</v>
+        <v>2513</v>
       </c>
       <c r="F1294">
         <v>70</v>
       </c>
       <c r="G1294" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="H1294" s="1" t="s">
-        <v>2578</v>
+        <v>2518</v>
       </c>
       <c r="J1294" s="1" t="s">
-        <v>871</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1295" spans="1:10">
       <c r="A1295" t="s">
-        <v>2569</v>
+        <v>2508</v>
       </c>
       <c r="B1295" t="s">
-        <v>2570</v>
+        <v>2510</v>
       </c>
       <c r="C1295" t="s">
-        <v>2574</v>
+        <v>2517</v>
       </c>
       <c r="D1295" t="s">
-        <v>2575</v>
+        <v>2514</v>
       </c>
       <c r="E1295" t="s">
-        <v>2576</v>
+        <v>2515</v>
       </c>
       <c r="F1295">
         <v>70</v>
@@ -57434,68 +57566,68 @@
         <v>340</v>
       </c>
       <c r="H1295" s="1" t="s">
-        <v>2579</v>
+        <v>2519</v>
       </c>
       <c r="J1295" s="1" t="s">
-        <v>2577</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="1296" spans="1:10">
       <c r="A1296" t="s">
-        <v>2541</v>
+        <v>2569</v>
       </c>
       <c r="B1296" t="s">
-        <v>2542</v>
+        <v>2570</v>
       </c>
       <c r="C1296" t="s">
-        <v>2543</v>
+        <v>2571</v>
       </c>
       <c r="D1296" t="s">
-        <v>2544</v>
+        <v>2572</v>
       </c>
       <c r="E1296" t="s">
-        <v>2545</v>
+        <v>2573</v>
       </c>
       <c r="F1296">
         <v>70</v>
       </c>
       <c r="G1296" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H1296" s="1" t="s">
-        <v>2535</v>
+        <v>2578</v>
       </c>
       <c r="J1296" s="1" t="s">
-        <v>1276</v>
+        <v>871</v>
       </c>
     </row>
     <row r="1297" spans="1:10">
       <c r="A1297" t="s">
-        <v>2541</v>
+        <v>2569</v>
       </c>
       <c r="B1297" t="s">
-        <v>2542</v>
+        <v>2570</v>
       </c>
       <c r="C1297" t="s">
-        <v>2546</v>
+        <v>2574</v>
       </c>
       <c r="D1297" t="s">
-        <v>2553</v>
+        <v>2575</v>
       </c>
       <c r="E1297" t="s">
-        <v>2554</v>
+        <v>2576</v>
       </c>
       <c r="F1297">
         <v>70</v>
       </c>
       <c r="G1297" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H1297" s="1" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="J1297" s="1" t="s">
-        <v>2467</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="1298" spans="1:10">
@@ -57506,19 +57638,19 @@
         <v>2542</v>
       </c>
       <c r="C1298" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="D1298" t="s">
-        <v>2555</v>
+        <v>2544</v>
       </c>
       <c r="E1298" t="s">
-        <v>2556</v>
+        <v>2545</v>
       </c>
       <c r="F1298">
         <v>70</v>
       </c>
       <c r="G1298" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H1298" s="1" t="s">
         <v>2535</v>
@@ -57535,19 +57667,19 @@
         <v>2542</v>
       </c>
       <c r="C1299" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="D1299" t="s">
-        <v>2557</v>
+        <v>2553</v>
       </c>
       <c r="E1299" t="s">
-        <v>2558</v>
+        <v>2554</v>
       </c>
       <c r="F1299">
         <v>70</v>
       </c>
       <c r="G1299" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H1299" s="1" t="s">
         <v>2567</v>
@@ -57564,13 +57696,13 @@
         <v>2542</v>
       </c>
       <c r="C1300" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="D1300" t="s">
-        <v>2559</v>
+        <v>2555</v>
       </c>
       <c r="E1300" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="F1300">
         <v>70</v>
@@ -57582,7 +57714,7 @@
         <v>2535</v>
       </c>
       <c r="J1300" s="1" t="s">
-        <v>2461</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1301" spans="1:10">
@@ -57593,19 +57725,19 @@
         <v>2542</v>
       </c>
       <c r="C1301" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="D1301" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="E1301" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="F1301">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G1301" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H1301" s="1" t="s">
         <v>2567</v>
@@ -57622,25 +57754,25 @@
         <v>2542</v>
       </c>
       <c r="C1302" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="D1302" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="E1302" t="s">
-        <v>2563</v>
+        <v>2559</v>
       </c>
       <c r="F1302">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1302" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H1302" s="1" t="s">
-        <v>2568</v>
+        <v>2535</v>
       </c>
       <c r="J1302" s="1" t="s">
-        <v>2566</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="1303" spans="1:10">
@@ -57651,83 +57783,83 @@
         <v>2542</v>
       </c>
       <c r="C1303" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="D1303" t="s">
-        <v>2564</v>
+        <v>2560</v>
       </c>
       <c r="E1303" t="s">
-        <v>2565</v>
+        <v>2561</v>
       </c>
       <c r="F1303">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G1303" s="3" t="s">
         <v>341</v>
       </c>
       <c r="H1303" s="1" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="J1303" s="1" t="s">
-        <v>2566</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="1304" spans="1:10">
       <c r="A1304" t="s">
-        <v>2520</v>
+        <v>2541</v>
       </c>
       <c r="B1304" t="s">
-        <v>2521</v>
+        <v>2542</v>
       </c>
       <c r="C1304" t="s">
-        <v>2522</v>
+        <v>2551</v>
       </c>
       <c r="D1304" t="s">
-        <v>2523</v>
+        <v>2562</v>
       </c>
       <c r="E1304" t="s">
-        <v>2523</v>
+        <v>2563</v>
       </c>
       <c r="F1304">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G1304" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H1304" s="1" t="s">
-        <v>2531</v>
+        <v>2568</v>
       </c>
       <c r="J1304" s="1" t="s">
-        <v>2527</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="1305" spans="1:10">
       <c r="A1305" t="s">
-        <v>2520</v>
+        <v>2541</v>
       </c>
       <c r="B1305" t="s">
-        <v>2521</v>
+        <v>2542</v>
       </c>
       <c r="C1305" t="s">
-        <v>2537</v>
+        <v>2552</v>
       </c>
       <c r="D1305" t="s">
-        <v>2524</v>
+        <v>2564</v>
       </c>
       <c r="E1305" t="s">
-        <v>2536</v>
+        <v>2565</v>
       </c>
       <c r="F1305">
         <v>60</v>
       </c>
       <c r="G1305" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1305" s="1" t="s">
-        <v>2532</v>
+        <v>2568</v>
       </c>
       <c r="J1305" s="1" t="s">
-        <v>2528</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="1306" spans="1:10">
@@ -57738,25 +57870,25 @@
         <v>2521</v>
       </c>
       <c r="C1306" t="s">
-        <v>2538</v>
+        <v>2522</v>
       </c>
       <c r="D1306" t="s">
-        <v>3298</v>
+        <v>2523</v>
       </c>
       <c r="E1306" t="s">
-        <v>3299</v>
+        <v>2523</v>
       </c>
       <c r="F1306">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="G1306" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="H1306" s="1" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="J1306" s="1" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="1307" spans="1:10">
@@ -57767,25 +57899,25 @@
         <v>2521</v>
       </c>
       <c r="C1307" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="D1307" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="E1307" t="s">
-        <v>2525</v>
+        <v>2536</v>
       </c>
       <c r="F1307">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G1307" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H1307" s="1" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="J1307" s="1" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="1308" spans="1:10">
@@ -57796,141 +57928,141 @@
         <v>2521</v>
       </c>
       <c r="C1308" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="D1308" t="s">
-        <v>2526</v>
+        <v>3298</v>
       </c>
       <c r="E1308" t="s">
-        <v>2580</v>
+        <v>3299</v>
       </c>
       <c r="F1308">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G1308" s="3" t="s">
-        <v>1905</v>
+        <v>335</v>
       </c>
       <c r="H1308" s="1" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="J1308" s="1" t="s">
-        <v>1276</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="1309" spans="1:10">
       <c r="A1309" t="s">
-        <v>375</v>
+        <v>2520</v>
       </c>
       <c r="B1309" t="s">
-        <v>28</v>
+        <v>2521</v>
       </c>
       <c r="C1309" t="s">
-        <v>376</v>
+        <v>2539</v>
       </c>
       <c r="D1309" t="s">
-        <v>377</v>
+        <v>2525</v>
       </c>
       <c r="E1309" t="s">
-        <v>422</v>
+        <v>2525</v>
       </c>
       <c r="F1309">
         <v>75</v>
       </c>
       <c r="G1309" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H1309" s="1" t="s">
-        <v>378</v>
+        <v>2534</v>
       </c>
       <c r="J1309" s="1" t="s">
-        <v>378</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="1310" spans="1:10">
       <c r="A1310" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>2526</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F1310">
+        <v>60</v>
+      </c>
+      <c r="G1310" s="3" t="s">
+        <v>1905</v>
+      </c>
+      <c r="H1310" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="J1310" s="1" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:10">
+      <c r="A1311" t="s">
         <v>375</v>
       </c>
-      <c r="B1310" t="s">
+      <c r="B1311" t="s">
         <v>28</v>
       </c>
-      <c r="C1310" t="s">
+      <c r="C1311" t="s">
+        <v>376</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>377</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>422</v>
+      </c>
+      <c r="F1311">
+        <v>75</v>
+      </c>
+      <c r="G1311" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H1311" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J1311" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:10">
+      <c r="A1312" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1312" t="s">
         <v>2608</v>
       </c>
-      <c r="D1310" t="s">
+      <c r="D1312" t="s">
         <v>1665</v>
       </c>
-      <c r="E1310" t="s">
+      <c r="E1312" t="s">
         <v>423</v>
       </c>
-      <c r="F1310">
+      <c r="F1312">
         <v>75</v>
       </c>
-      <c r="G1310" s="3" t="s">
+      <c r="G1312" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="H1310" s="1" t="s">
+      <c r="H1312" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="J1310" s="1" t="s">
+      <c r="J1312" s="1" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="1311" spans="1:10">
-      <c r="A1311" s="8" t="s">
-        <v>5105</v>
-      </c>
-      <c r="B1311" s="9" t="s">
-        <v>5106</v>
-      </c>
-      <c r="C1311" s="8" t="s">
-        <v>5107</v>
-      </c>
-      <c r="D1311" t="s">
-        <v>5108</v>
-      </c>
-      <c r="E1311" t="s">
-        <v>5108</v>
-      </c>
-      <c r="F1311">
-        <v>60</v>
-      </c>
-      <c r="G1311" s="3" t="s">
-        <v>5115</v>
-      </c>
-      <c r="H1311" s="1" t="s">
-        <v>5116</v>
-      </c>
-      <c r="J1311" s="1" t="s">
-        <v>5116</v>
-      </c>
-    </row>
-    <row r="1312" spans="1:10">
-      <c r="A1312" s="8" t="s">
-        <v>5105</v>
-      </c>
-      <c r="B1312" s="9" t="s">
-        <v>5106</v>
-      </c>
-      <c r="C1312" s="8" t="s">
-        <v>5112</v>
-      </c>
-      <c r="D1312" t="s">
-        <v>5109</v>
-      </c>
-      <c r="E1312" t="s">
-        <v>5109</v>
-      </c>
-      <c r="F1312">
-        <v>80</v>
-      </c>
-      <c r="G1312" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H1312" s="1" t="s">
-        <v>5117</v>
-      </c>
-      <c r="J1312" s="1" t="s">
-        <v>5117</v>
       </c>
     </row>
     <row r="1313" spans="1:10">
@@ -57941,25 +58073,25 @@
         <v>5106</v>
       </c>
       <c r="C1313" s="8" t="s">
-        <v>5113</v>
+        <v>5107</v>
       </c>
       <c r="D1313" t="s">
-        <v>5110</v>
+        <v>5108</v>
       </c>
       <c r="E1313" t="s">
-        <v>5110</v>
+        <v>5108</v>
       </c>
       <c r="F1313">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G1313" s="3" t="s">
-        <v>1347</v>
+        <v>5115</v>
       </c>
       <c r="H1313" s="1" t="s">
-        <v>5118</v>
+        <v>5116</v>
       </c>
       <c r="J1313" s="1" t="s">
-        <v>5119</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="1314" spans="1:10">
@@ -57970,83 +58102,83 @@
         <v>5106</v>
       </c>
       <c r="C1314" s="8" t="s">
-        <v>5114</v>
+        <v>5112</v>
       </c>
       <c r="D1314" t="s">
-        <v>5111</v>
+        <v>5109</v>
       </c>
       <c r="E1314" t="s">
-        <v>5111</v>
+        <v>5109</v>
       </c>
       <c r="F1314">
         <v>80</v>
       </c>
       <c r="G1314" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H1314" s="1" t="s">
-        <v>5120</v>
+        <v>5117</v>
       </c>
       <c r="J1314" s="1" t="s">
-        <v>5121</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="1315" spans="1:10">
       <c r="A1315" s="8" t="s">
-        <v>5122</v>
+        <v>5105</v>
       </c>
       <c r="B1315" s="9" t="s">
-        <v>5123</v>
+        <v>5106</v>
       </c>
       <c r="C1315" s="8" t="s">
-        <v>5124</v>
+        <v>5113</v>
       </c>
       <c r="D1315" t="s">
-        <v>5125</v>
+        <v>5110</v>
       </c>
       <c r="E1315" t="s">
-        <v>5125</v>
+        <v>5110</v>
       </c>
       <c r="F1315">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G1315" s="3" t="s">
-        <v>340</v>
+        <v>1347</v>
       </c>
       <c r="H1315" s="1" t="s">
-        <v>5129</v>
+        <v>5118</v>
       </c>
       <c r="J1315" s="1" t="s">
-        <v>5129</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="1316" spans="1:10">
       <c r="A1316" s="8" t="s">
-        <v>5122</v>
+        <v>5105</v>
       </c>
       <c r="B1316" s="9" t="s">
-        <v>5123</v>
+        <v>5106</v>
       </c>
       <c r="C1316" s="8" t="s">
-        <v>5132</v>
+        <v>5114</v>
       </c>
       <c r="D1316" t="s">
-        <v>5126</v>
+        <v>5111</v>
       </c>
       <c r="E1316" t="s">
-        <v>5126</v>
+        <v>5111</v>
       </c>
       <c r="F1316">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G1316" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H1316" s="1" t="s">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="J1316" s="1" t="s">
-        <v>5130</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="1317" spans="1:10">
@@ -58057,71 +58189,71 @@
         <v>5123</v>
       </c>
       <c r="C1317" s="8" t="s">
-        <v>5133</v>
+        <v>5124</v>
       </c>
       <c r="D1317" t="s">
-        <v>5127</v>
+        <v>5125</v>
       </c>
       <c r="E1317" t="s">
-        <v>5128</v>
+        <v>5125</v>
       </c>
       <c r="F1317">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G1317" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1317" s="1" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="J1317" s="1" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="1318" spans="1:10">
       <c r="A1318" s="8" t="s">
-        <v>5134</v>
+        <v>5122</v>
       </c>
       <c r="B1318" s="9" t="s">
-        <v>5135</v>
+        <v>5123</v>
       </c>
       <c r="C1318" s="8" t="s">
-        <v>5136</v>
+        <v>5132</v>
       </c>
       <c r="D1318" t="s">
-        <v>5137</v>
+        <v>5126</v>
       </c>
       <c r="E1318" t="s">
-        <v>5137</v>
+        <v>5126</v>
       </c>
       <c r="F1318">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G1318" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1318" s="1" t="s">
-        <v>5146</v>
+        <v>5130</v>
       </c>
       <c r="J1318" s="1" t="s">
-        <v>5146</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="1319" spans="1:10">
       <c r="A1319" s="8" t="s">
-        <v>5134</v>
+        <v>5122</v>
       </c>
       <c r="B1319" s="9" t="s">
-        <v>5135</v>
+        <v>5123</v>
       </c>
       <c r="C1319" s="8" t="s">
-        <v>5142</v>
+        <v>5133</v>
       </c>
       <c r="D1319" t="s">
-        <v>5138</v>
+        <v>5127</v>
       </c>
       <c r="E1319" t="s">
-        <v>5138</v>
+        <v>5128</v>
       </c>
       <c r="F1319">
         <v>60</v>
@@ -58130,10 +58262,10 @@
         <v>345</v>
       </c>
       <c r="H1319" s="1" t="s">
-        <v>5147</v>
+        <v>5131</v>
       </c>
       <c r="J1319" s="1" t="s">
-        <v>5147</v>
+        <v>5131</v>
       </c>
     </row>
     <row r="1320" spans="1:10">
@@ -58144,13 +58276,13 @@
         <v>5135</v>
       </c>
       <c r="C1320" s="8" t="s">
-        <v>5143</v>
+        <v>5136</v>
       </c>
       <c r="D1320" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="E1320" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="F1320">
         <v>60</v>
@@ -58159,10 +58291,10 @@
         <v>345</v>
       </c>
       <c r="H1320" s="1" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="J1320" s="1" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
     </row>
     <row r="1321" spans="1:10">
@@ -58173,13 +58305,13 @@
         <v>5135</v>
       </c>
       <c r="C1321" s="8" t="s">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="D1321" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="E1321" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="F1321">
         <v>60</v>
@@ -58188,10 +58320,10 @@
         <v>345</v>
       </c>
       <c r="H1321" s="1" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
       <c r="J1321" s="1" t="s">
-        <v>5146</v>
+        <v>5147</v>
       </c>
     </row>
     <row r="1322" spans="1:10">
@@ -58202,13 +58334,13 @@
         <v>5135</v>
       </c>
       <c r="C1322" s="8" t="s">
-        <v>5145</v>
+        <v>5143</v>
       </c>
       <c r="D1322" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="E1322" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="F1322">
         <v>60</v>
@@ -58217,16 +58349,103 @@
         <v>345</v>
       </c>
       <c r="H1322" s="1" t="s">
+        <v>5148</v>
+      </c>
+      <c r="J1322" s="1" t="s">
+        <v>5148</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:10">
+      <c r="A1323" s="8" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B1323" s="9" t="s">
+        <v>5135</v>
+      </c>
+      <c r="C1323" s="8" t="s">
+        <v>5144</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>5140</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>5140</v>
+      </c>
+      <c r="F1323">
+        <v>60</v>
+      </c>
+      <c r="G1323" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H1323" s="1" t="s">
         <v>5146</v>
       </c>
-      <c r="J1322" s="1" t="s">
+      <c r="J1323" s="1" t="s">
+        <v>5146</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:10">
+      <c r="A1324" s="8" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B1324" s="9" t="s">
+        <v>5135</v>
+      </c>
+      <c r="C1324" s="8" t="s">
+        <v>5145</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>5141</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>5141</v>
+      </c>
+      <c r="F1324">
+        <v>60</v>
+      </c>
+      <c r="G1324" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H1324" s="1" t="s">
+        <v>5146</v>
+      </c>
+      <c r="J1324" s="1" t="s">
         <v>5147</v>
       </c>
     </row>
+    <row r="1325" spans="1:10">
+      <c r="A1325" s="8" t="s">
+        <v>5160</v>
+      </c>
+      <c r="B1325" s="9" t="s">
+        <v>5161</v>
+      </c>
+      <c r="C1325" s="8" t="s">
+        <v>5166</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>5162</v>
+      </c>
+      <c r="E1325" t="s">
+        <v>5162</v>
+      </c>
+      <c r="F1325">
+        <v>85</v>
+      </c>
+      <c r="G1325" s="3" t="s">
+        <v>5163</v>
+      </c>
+      <c r="H1325" s="1" t="s">
+        <v>5164</v>
+      </c>
+      <c r="J1325" s="1" t="s">
+        <v>5165</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1310">
-    <sortCondition ref="B2:B1310"/>
-    <sortCondition ref="C2:C1310"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1312">
+    <sortCondition ref="B2:B1312"/>
+    <sortCondition ref="C2:C1312"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F38577A-EA4C-4958-9EB4-759E2B4BA646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715F22FD-4999-47EB-8F64-B970538F83DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
   <sheets>
     <sheet name="themes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11149" uniqueCount="5446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11185" uniqueCount="5465">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -20491,6 +20491,77 @@
   </si>
   <si>
     <t>어느날알바를마치고집에왔는데돈도없고밥도없고공모전엔또떨어져서진짜답도없고있는게아무것도없네하고감성에젖다가자려고했는데갑자기모니터에서...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sh_nbc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>셜록홈즈 뉴부천점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sh_nbc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sh_nbc2</t>
+  </si>
+  <si>
+    <t>sh_nbc3</t>
+  </si>
+  <si>
+    <t>sh_nbc4</t>
+  </si>
+  <si>
+    <t>sh_nbc5</t>
+  </si>
+  <si>
+    <t>sh_nbc6</t>
+  </si>
+  <si>
+    <t>MADEON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XIAMEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOUNDRED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월간오컬트 : 폐간호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MADEON,마데온</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XIAMEN,샤먼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOUNDRED,하운드레드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRACK,크랙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1분당 350원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -20992,7 +21063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6A8B62-C038-47D4-9D17-9A5AC9BFE2AE}">
-  <dimension ref="A1:L1395"/>
+  <dimension ref="A1:L1401"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
@@ -61529,6 +61600,144 @@
       </c>
       <c r="J1395" s="1" t="s">
         <v>318</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:10">
+      <c r="A1396" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1396" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>5448</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>5454</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>5460</v>
+      </c>
+      <c r="F1396">
+        <v>70</v>
+      </c>
+      <c r="G1396" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:10">
+      <c r="A1397" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1397" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>5449</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>5455</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>5461</v>
+      </c>
+      <c r="F1397">
+        <v>60</v>
+      </c>
+      <c r="G1397" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:10">
+      <c r="A1398" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1398" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>5450</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>5456</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>5462</v>
+      </c>
+      <c r="F1398">
+        <v>60</v>
+      </c>
+      <c r="G1398" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:10">
+      <c r="A1399" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1399" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>5451</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>5457</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>5463</v>
+      </c>
+      <c r="F1399">
+        <v>60</v>
+      </c>
+      <c r="G1399" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:10">
+      <c r="A1400" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1400" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>5452</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>5458</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>5458</v>
+      </c>
+      <c r="F1400">
+        <v>60</v>
+      </c>
+      <c r="G1400" s="3" t="s">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:10">
+      <c r="A1401" s="8" t="s">
+        <v>5446</v>
+      </c>
+      <c r="B1401" s="9" t="s">
+        <v>5447</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>5453</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>5459</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>5459</v>
+      </c>
+      <c r="F1401">
+        <v>60</v>
+      </c>
+      <c r="G1401" s="3" t="s">
+        <v>5464</v>
       </c>
     </row>
   </sheetData>

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C3E8B1-7CB0-40F4-B40A-A75946F5803B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4A4344-BAAE-4FD7-8C48-B3E368FB20A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29010" yWindow="3045" windowWidth="14610" windowHeight="10770" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
   <sheets>
     <sheet name="themes" sheetId="1" r:id="rId1"/>
@@ -36889,7 +36889,7 @@
         <v>50</v>
       </c>
       <c r="G529" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H529" s="1" t="s">
         <v>1195</v>
@@ -36918,7 +36918,7 @@
         <v>60</v>
       </c>
       <c r="G530" s="3" t="s">
-        <v>1196</v>
+        <v>342</v>
       </c>
       <c r="H530" s="1" t="s">
         <v>1198</v>
@@ -36947,7 +36947,7 @@
         <v>60</v>
       </c>
       <c r="G531" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H531" s="1" t="s">
         <v>1197</v>
@@ -36976,7 +36976,7 @@
         <v>60</v>
       </c>
       <c r="G532" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H532" s="1" t="s">
         <v>646</v>

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F4D2F5-527A-4A61-81A2-5C02A628A3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF26C316-EB16-4DF5-8D2A-1DDA9125A119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
+    <workbookView xWindow="720" yWindow="1410" windowWidth="21600" windowHeight="11835" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
   <sheets>
     <sheet name="themes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -42,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11550" uniqueCount="5609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11553" uniqueCount="5609">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -29763,6 +29754,15 @@
       <c r="F282">
         <v>60</v>
       </c>
+      <c r="G282" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="H282" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="283" spans="1:10">
       <c r="A283" t="s">

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A44B20-4220-44F1-B4EE-68CFA0FBEA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF54166-B3D7-4A23-812A-155F10707B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11670" uniqueCount="5648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11670" uniqueCount="5646">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -20838,13 +20838,6 @@
   <si>
     <t>데이투어,DAYTOUR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1100,1230,1530,1715,1900,2100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1200,1400,1530,1830,2015,2200</t>
   </si>
   <si>
     <t>ft_str3_2</t>
@@ -21914,19 +21907,19 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="8" t="s">
+        <v>5545</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>5546</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>5547</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="D6" t="s">
         <v>5548</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>5549</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5550</v>
-      </c>
       <c r="E6" t="s">
-        <v>5550</v>
+        <v>5548</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -24425,19 +24418,19 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="8" t="s">
-        <v>5583</v>
+        <v>5581</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>5574</v>
+        <v>5572</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>5584</v>
+        <v>5582</v>
       </c>
       <c r="D93" t="s">
-        <v>5546</v>
+        <v>5544</v>
       </c>
       <c r="E93" t="s">
-        <v>5546</v>
+        <v>5544</v>
       </c>
       <c r="F93">
         <v>65</v>
@@ -24446,7 +24439,7 @@
         <v>329</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>5586</v>
+        <v>5584</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>1001</v>
@@ -24454,19 +24447,19 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="8" t="s">
+        <v>5581</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>5572</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>5583</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>5574</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>5585</v>
-      </c>
       <c r="D94" t="s">
-        <v>5573</v>
+        <v>5571</v>
       </c>
       <c r="E94" t="s">
-        <v>5573</v>
+        <v>5571</v>
       </c>
       <c r="F94">
         <v>60</v>
@@ -24475,21 +24468,21 @@
         <v>335</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>5587</v>
+        <v>5585</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>5588</v>
+        <v>5586</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B95" t="s">
         <v>3581</v>
       </c>
       <c r="C95" t="s">
-        <v>5575</v>
+        <v>5573</v>
       </c>
       <c r="D95" t="s">
         <v>1564</v>
@@ -24512,13 +24505,13 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B96" t="s">
         <v>3581</v>
       </c>
       <c r="C96" t="s">
-        <v>5576</v>
+        <v>5574</v>
       </c>
       <c r="D96" t="s">
         <v>1572</v>
@@ -24541,13 +24534,13 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B97" t="s">
         <v>3581</v>
       </c>
       <c r="C97" t="s">
-        <v>5577</v>
+        <v>5575</v>
       </c>
       <c r="D97" t="s">
         <v>1569</v>
@@ -24570,13 +24563,13 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B98" t="s">
         <v>3581</v>
       </c>
       <c r="C98" t="s">
-        <v>5578</v>
+        <v>5576</v>
       </c>
       <c r="D98" t="s">
         <v>1568</v>
@@ -24599,13 +24592,13 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B99" t="s">
         <v>3581</v>
       </c>
       <c r="C99" t="s">
-        <v>5579</v>
+        <v>5577</v>
       </c>
       <c r="D99" t="s">
         <v>1565</v>
@@ -24628,13 +24621,13 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B100" t="s">
         <v>3581</v>
       </c>
       <c r="C100" t="s">
-        <v>5580</v>
+        <v>5578</v>
       </c>
       <c r="D100" t="s">
         <v>1566</v>
@@ -24657,13 +24650,13 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>5582</v>
+        <v>5580</v>
       </c>
       <c r="B101" t="s">
         <v>3581</v>
       </c>
       <c r="C101" t="s">
-        <v>5581</v>
+        <v>5579</v>
       </c>
       <c r="D101" t="s">
         <v>1567</v>
@@ -27998,13 +27991,13 @@
         <v>1072</v>
       </c>
       <c r="C216" t="s">
-        <v>5565</v>
+        <v>5563</v>
       </c>
       <c r="D216" t="s">
-        <v>5566</v>
+        <v>5564</v>
       </c>
       <c r="E216" t="s">
-        <v>5566</v>
+        <v>5564</v>
       </c>
       <c r="F216">
         <v>60</v>
@@ -28013,7 +28006,7 @@
         <v>338</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>5567</v>
+        <v>5565</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>170</v>
@@ -28027,13 +28020,13 @@
         <v>1072</v>
       </c>
       <c r="C217" t="s">
+        <v>5566</v>
+      </c>
+      <c r="D217" t="s">
+        <v>5567</v>
+      </c>
+      <c r="E217" t="s">
         <v>5568</v>
-      </c>
-      <c r="D217" t="s">
-        <v>5569</v>
-      </c>
-      <c r="E217" t="s">
-        <v>5570</v>
       </c>
       <c r="F217">
         <v>60</v>
@@ -28671,10 +28664,10 @@
         <v>333</v>
       </c>
       <c r="H239" s="1" t="s">
-        <v>5541</v>
+        <v>4997</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>5541</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -28700,10 +28693,10 @@
         <v>333</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>5542</v>
+        <v>702</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>5542</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -29894,13 +29887,13 @@
         <v>994</v>
       </c>
       <c r="C282" t="s">
-        <v>5571</v>
+        <v>5569</v>
       </c>
       <c r="D282" t="s">
-        <v>5591</v>
+        <v>5589</v>
       </c>
       <c r="E282" t="s">
-        <v>5639</v>
+        <v>5637</v>
       </c>
       <c r="F282">
         <v>60</v>
@@ -35851,7 +35844,7 @@
         <v>3310</v>
       </c>
       <c r="B487" s="9" t="s">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C487" s="8" t="s">
         <v>3357</v>
@@ -35880,7 +35873,7 @@
         <v>3310</v>
       </c>
       <c r="B488" s="9" t="s">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C488" s="8" t="s">
         <v>3358</v>
@@ -35909,7 +35902,7 @@
         <v>3310</v>
       </c>
       <c r="B489" s="9" t="s">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C489" s="8" t="s">
         <v>3359</v>
@@ -35938,7 +35931,7 @@
         <v>3310</v>
       </c>
       <c r="B490" s="9" t="s">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C490" s="8" t="s">
         <v>3360</v>
@@ -35967,7 +35960,7 @@
         <v>3307</v>
       </c>
       <c r="B491" s="9" t="s">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C491" s="8" t="s">
         <v>3336</v>
@@ -35996,7 +35989,7 @@
         <v>3307</v>
       </c>
       <c r="B492" s="9" t="s">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C492" s="8" t="s">
         <v>3337</v>
@@ -36025,7 +36018,7 @@
         <v>3307</v>
       </c>
       <c r="B493" s="9" t="s">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C493" s="8" t="s">
         <v>3338</v>
@@ -36054,7 +36047,7 @@
         <v>3307</v>
       </c>
       <c r="B494" s="9" t="s">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C494" s="8" t="s">
         <v>3339</v>
@@ -36083,7 +36076,7 @@
         <v>3307</v>
       </c>
       <c r="B495" s="9" t="s">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C495" s="8" t="s">
         <v>3340</v>
@@ -36478,7 +36471,7 @@
         <v>3663</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>5572</v>
+        <v>5570</v>
       </c>
       <c r="J508" s="1" t="s">
         <v>2641</v>
@@ -36985,13 +36978,13 @@
         <v>478</v>
       </c>
       <c r="C526" t="s">
+        <v>5638</v>
+      </c>
+      <c r="D526" t="s">
         <v>5640</v>
       </c>
-      <c r="D526" t="s">
-        <v>5642</v>
-      </c>
       <c r="E526" t="s">
-        <v>5643</v>
+        <v>5641</v>
       </c>
       <c r="F526">
         <v>70</v>
@@ -37000,7 +36993,7 @@
         <v>336</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>5641</v>
+        <v>5639</v>
       </c>
       <c r="J526" s="1" t="s">
         <v>2026</v>
@@ -41325,7 +41318,7 @@
         <v>3574</v>
       </c>
       <c r="J674" s="1" t="s">
-        <v>5557</v>
+        <v>5555</v>
       </c>
     </row>
     <row r="675" spans="1:10">
@@ -42682,7 +42675,7 @@
         <v>5244</v>
       </c>
       <c r="J721" s="1" t="s">
-        <v>5556</v>
+        <v>5554</v>
       </c>
     </row>
     <row r="722" spans="1:10">
@@ -45448,7 +45441,7 @@
         <v>3889</v>
       </c>
       <c r="E817" t="s">
-        <v>5553</v>
+        <v>5551</v>
       </c>
       <c r="F817">
         <v>60</v>
@@ -45564,7 +45557,7 @@
         <v>60</v>
       </c>
       <c r="G821" s="3" t="s">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="H821" s="1" t="s">
         <v>1760</v>
@@ -45804,7 +45797,7 @@
         <v>5506</v>
       </c>
       <c r="B830" s="9" t="s">
-        <v>5551</v>
+        <v>5549</v>
       </c>
       <c r="C830" s="8" t="s">
         <v>5507</v>
@@ -45822,7 +45815,7 @@
         <v>5516</v>
       </c>
       <c r="H830" s="1" t="s">
-        <v>5589</v>
+        <v>5587</v>
       </c>
       <c r="J830" s="1" t="s">
         <v>1627</v>
@@ -45833,7 +45826,7 @@
         <v>5506</v>
       </c>
       <c r="B831" s="9" t="s">
-        <v>5551</v>
+        <v>5549</v>
       </c>
       <c r="C831" s="8" t="s">
         <v>5517</v>
@@ -45862,7 +45855,7 @@
         <v>5506</v>
       </c>
       <c r="B832" s="9" t="s">
-        <v>5551</v>
+        <v>5549</v>
       </c>
       <c r="C832" s="8" t="s">
         <v>5518</v>
@@ -45891,7 +45884,7 @@
         <v>5506</v>
       </c>
       <c r="B833" s="9" t="s">
-        <v>5551</v>
+        <v>5549</v>
       </c>
       <c r="C833" s="8" t="s">
         <v>5519</v>
@@ -45920,7 +45913,7 @@
         <v>5506</v>
       </c>
       <c r="B834" s="9" t="s">
-        <v>5551</v>
+        <v>5549</v>
       </c>
       <c r="C834" s="8" t="s">
         <v>5520</v>
@@ -45938,7 +45931,7 @@
         <v>5516</v>
       </c>
       <c r="H834" s="1" t="s">
-        <v>5590</v>
+        <v>5588</v>
       </c>
       <c r="J834" s="1" t="s">
         <v>1686</v>
@@ -51730,10 +51723,10 @@
         <v>5178</v>
       </c>
       <c r="D1033" t="s">
-        <v>5554</v>
+        <v>5552</v>
       </c>
       <c r="E1033" t="s">
-        <v>5554</v>
+        <v>5552</v>
       </c>
       <c r="F1033">
         <v>60</v>
@@ -51742,7 +51735,7 @@
         <v>342</v>
       </c>
       <c r="H1033" s="1" t="s">
-        <v>5555</v>
+        <v>5553</v>
       </c>
       <c r="J1033" s="1" t="s">
         <v>2029</v>
@@ -53003,13 +52996,13 @@
         <v>2280</v>
       </c>
       <c r="C1077" t="s">
+        <v>5590</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>5591</v>
+      </c>
+      <c r="E1077" t="s">
         <v>5592</v>
-      </c>
-      <c r="D1077" t="s">
-        <v>5593</v>
-      </c>
-      <c r="E1077" t="s">
-        <v>5594</v>
       </c>
       <c r="F1077">
         <v>60</v>
@@ -60170,13 +60163,13 @@
         <v>3430</v>
       </c>
       <c r="C1323" s="8" t="s">
-        <v>5543</v>
+        <v>5541</v>
       </c>
       <c r="D1323" s="8" t="s">
-        <v>5544</v>
+        <v>5542</v>
       </c>
       <c r="E1323" s="8" t="s">
-        <v>5544</v>
+        <v>5542</v>
       </c>
       <c r="F1323">
         <v>80</v>
@@ -60188,7 +60181,7 @@
         <v>321</v>
       </c>
       <c r="J1323" s="1" t="s">
-        <v>5545</v>
+        <v>5543</v>
       </c>
     </row>
     <row r="1324" spans="1:12">
@@ -62029,10 +62022,10 @@
         <v>1995</v>
       </c>
       <c r="D1387" t="s">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="E1387" t="s">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="F1387">
         <v>60</v>
@@ -63670,13 +63663,13 @@
         <v>5522</v>
       </c>
       <c r="C1444" s="8" t="s">
+        <v>5642</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>5643</v>
+      </c>
+      <c r="E1444" t="s">
         <v>5644</v>
-      </c>
-      <c r="D1444" t="s">
-        <v>5645</v>
-      </c>
-      <c r="E1444" t="s">
-        <v>5646</v>
       </c>
       <c r="F1444">
         <v>60</v>
@@ -63751,31 +63744,31 @@
     </row>
     <row r="1447" spans="1:11">
       <c r="A1447" s="8" t="s">
+        <v>5556</v>
+      </c>
+      <c r="B1447" s="9" t="s">
+        <v>5557</v>
+      </c>
+      <c r="C1447" s="8" t="s">
         <v>5558</v>
       </c>
-      <c r="B1447" s="9" t="s">
+      <c r="D1447" t="s">
         <v>5559</v>
       </c>
-      <c r="C1447" s="8" t="s">
-        <v>5560</v>
-      </c>
-      <c r="D1447" t="s">
-        <v>5561</v>
-      </c>
       <c r="E1447" t="s">
-        <v>5561</v>
+        <v>5559</v>
       </c>
       <c r="F1447">
         <v>180</v>
       </c>
       <c r="G1447" s="3" t="s">
+        <v>5560</v>
+      </c>
+      <c r="H1447" s="1" t="s">
+        <v>5561</v>
+      </c>
+      <c r="J1447" s="1" t="s">
         <v>5562</v>
-      </c>
-      <c r="H1447" s="1" t="s">
-        <v>5563</v>
-      </c>
-      <c r="J1447" s="1" t="s">
-        <v>5564</v>
       </c>
       <c r="K1447">
         <v>5</v>
@@ -63783,19 +63776,19 @@
     </row>
     <row r="1448" spans="1:11">
       <c r="A1448" s="8" t="s">
+        <v>5593</v>
+      </c>
+      <c r="B1448" s="9" t="s">
+        <v>5594</v>
+      </c>
+      <c r="C1448" s="8" t="s">
         <v>5595</v>
       </c>
-      <c r="B1448" s="9" t="s">
-        <v>5596</v>
-      </c>
-      <c r="C1448" s="8" t="s">
-        <v>5597</v>
-      </c>
       <c r="D1448" t="s">
-        <v>5600</v>
+        <v>5598</v>
       </c>
       <c r="E1448" t="s">
-        <v>5600</v>
+        <v>5598</v>
       </c>
       <c r="F1448">
         <v>70</v>
@@ -63812,19 +63805,19 @@
     </row>
     <row r="1449" spans="1:11">
       <c r="A1449" s="8" t="s">
-        <v>5595</v>
+        <v>5593</v>
       </c>
       <c r="B1449" s="9" t="s">
+        <v>5594</v>
+      </c>
+      <c r="C1449" s="8" t="s">
         <v>5596</v>
       </c>
-      <c r="C1449" s="8" t="s">
-        <v>5598</v>
-      </c>
       <c r="D1449" t="s">
-        <v>5601</v>
+        <v>5599</v>
       </c>
       <c r="E1449" t="s">
-        <v>5601</v>
+        <v>5599</v>
       </c>
       <c r="F1449">
         <v>70</v>
@@ -63841,19 +63834,19 @@
     </row>
     <row r="1450" spans="1:11">
       <c r="A1450" s="8" t="s">
-        <v>5595</v>
+        <v>5593</v>
       </c>
       <c r="B1450" s="9" t="s">
-        <v>5596</v>
+        <v>5594</v>
       </c>
       <c r="C1450" s="8" t="s">
-        <v>5599</v>
+        <v>5597</v>
       </c>
       <c r="D1450" t="s">
-        <v>5602</v>
+        <v>5600</v>
       </c>
       <c r="E1450" t="s">
-        <v>5603</v>
+        <v>5601</v>
       </c>
       <c r="F1450">
         <v>70</v>
@@ -63870,19 +63863,19 @@
     </row>
     <row r="1451" spans="1:11">
       <c r="A1451" s="8" t="s">
+        <v>5605</v>
+      </c>
+      <c r="B1451" s="9" t="s">
+        <v>5606</v>
+      </c>
+      <c r="C1451" s="8" t="s">
         <v>5607</v>
       </c>
-      <c r="B1451" s="9" t="s">
-        <v>5608</v>
-      </c>
-      <c r="C1451" s="8" t="s">
-        <v>5609</v>
-      </c>
       <c r="D1451" t="s">
-        <v>5613</v>
+        <v>5611</v>
       </c>
       <c r="E1451" t="s">
-        <v>5617</v>
+        <v>5615</v>
       </c>
       <c r="F1451">
         <v>60</v>
@@ -63899,19 +63892,19 @@
     </row>
     <row r="1452" spans="1:11">
       <c r="A1452" s="8" t="s">
-        <v>5607</v>
+        <v>5605</v>
       </c>
       <c r="B1452" s="9" t="s">
+        <v>5606</v>
+      </c>
+      <c r="C1452" s="8" t="s">
         <v>5608</v>
       </c>
-      <c r="C1452" s="8" t="s">
-        <v>5610</v>
-      </c>
       <c r="D1452" t="s">
-        <v>5614</v>
+        <v>5612</v>
       </c>
       <c r="E1452" t="s">
-        <v>5618</v>
+        <v>5616</v>
       </c>
       <c r="F1452">
         <v>60</v>
@@ -63928,19 +63921,19 @@
     </row>
     <row r="1453" spans="1:11">
       <c r="A1453" s="8" t="s">
-        <v>5607</v>
+        <v>5605</v>
       </c>
       <c r="B1453" s="9" t="s">
-        <v>5608</v>
+        <v>5606</v>
       </c>
       <c r="C1453" s="8" t="s">
-        <v>5611</v>
+        <v>5609</v>
       </c>
       <c r="D1453" t="s">
-        <v>5615</v>
+        <v>5613</v>
       </c>
       <c r="E1453" t="s">
-        <v>5619</v>
+        <v>5617</v>
       </c>
       <c r="F1453">
         <v>60</v>
@@ -63949,27 +63942,27 @@
         <v>2271</v>
       </c>
       <c r="H1453" s="1" t="s">
-        <v>5621</v>
+        <v>5619</v>
       </c>
       <c r="J1453" s="1" t="s">
-        <v>5621</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="1454" spans="1:11">
       <c r="A1454" s="8" t="s">
-        <v>5607</v>
+        <v>5605</v>
       </c>
       <c r="B1454" s="9" t="s">
-        <v>5608</v>
+        <v>5606</v>
       </c>
       <c r="C1454" s="8" t="s">
-        <v>5612</v>
+        <v>5610</v>
       </c>
       <c r="D1454" t="s">
-        <v>5616</v>
+        <v>5614</v>
       </c>
       <c r="E1454" t="s">
-        <v>5620</v>
+        <v>5618</v>
       </c>
       <c r="F1454">
         <v>60</v>
@@ -63986,19 +63979,19 @@
     </row>
     <row r="1455" spans="1:11">
       <c r="A1455" t="s">
+        <v>5620</v>
+      </c>
+      <c r="B1455" s="9" t="s">
+        <v>5621</v>
+      </c>
+      <c r="C1455" t="s">
         <v>5622</v>
       </c>
-      <c r="B1455" s="9" t="s">
-        <v>5623</v>
-      </c>
-      <c r="C1455" t="s">
-        <v>5624</v>
-      </c>
       <c r="D1455" t="s">
-        <v>5632</v>
+        <v>5630</v>
       </c>
       <c r="E1455" t="s">
-        <v>5632</v>
+        <v>5630</v>
       </c>
       <c r="F1455">
         <v>60</v>
@@ -64015,19 +64008,19 @@
     </row>
     <row r="1456" spans="1:11">
       <c r="A1456" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1456" s="9" t="s">
+        <v>5621</v>
+      </c>
+      <c r="C1456" t="s">
         <v>5623</v>
       </c>
-      <c r="C1456" t="s">
-        <v>5625</v>
-      </c>
       <c r="D1456" t="s">
-        <v>5633</v>
+        <v>5631</v>
       </c>
       <c r="E1456" t="s">
-        <v>5633</v>
+        <v>5631</v>
       </c>
       <c r="F1456">
         <v>60</v>
@@ -64036,7 +64029,7 @@
         <v>3999</v>
       </c>
       <c r="H1456" s="1" t="s">
-        <v>5647</v>
+        <v>5645</v>
       </c>
       <c r="J1456" s="1" t="s">
         <v>2393</v>
@@ -64044,19 +64037,19 @@
     </row>
     <row r="1457" spans="1:10">
       <c r="A1457" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1457" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1457" t="s">
-        <v>5626</v>
+        <v>5624</v>
       </c>
       <c r="D1457" t="s">
-        <v>5634</v>
+        <v>5632</v>
       </c>
       <c r="E1457" t="s">
-        <v>5634</v>
+        <v>5632</v>
       </c>
       <c r="F1457">
         <v>60</v>
@@ -64073,19 +64066,19 @@
     </row>
     <row r="1458" spans="1:10">
       <c r="A1458" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1458" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1458" t="s">
-        <v>5627</v>
+        <v>5625</v>
       </c>
       <c r="D1458" t="s">
-        <v>5635</v>
+        <v>5633</v>
       </c>
       <c r="E1458" t="s">
-        <v>5635</v>
+        <v>5633</v>
       </c>
       <c r="F1458">
         <v>60</v>
@@ -64102,19 +64095,19 @@
     </row>
     <row r="1459" spans="1:10">
       <c r="A1459" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1459" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1459" t="s">
-        <v>5628</v>
+        <v>5626</v>
       </c>
       <c r="D1459" t="s">
-        <v>5636</v>
+        <v>5634</v>
       </c>
       <c r="E1459" t="s">
-        <v>5636</v>
+        <v>5634</v>
       </c>
       <c r="F1459">
         <v>70</v>
@@ -64125,19 +64118,19 @@
     </row>
     <row r="1460" spans="1:10">
       <c r="A1460" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1460" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1460" t="s">
-        <v>5629</v>
+        <v>5627</v>
       </c>
       <c r="D1460" t="s">
-        <v>5637</v>
+        <v>5635</v>
       </c>
       <c r="E1460" t="s">
-        <v>5637</v>
+        <v>5635</v>
       </c>
       <c r="F1460">
         <v>60</v>
@@ -64148,19 +64141,19 @@
     </row>
     <row r="1461" spans="1:10">
       <c r="A1461" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1461" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1461" t="s">
-        <v>5630</v>
+        <v>5628</v>
       </c>
       <c r="D1461" t="s">
-        <v>5638</v>
+        <v>5636</v>
       </c>
       <c r="E1461" t="s">
-        <v>5638</v>
+        <v>5636</v>
       </c>
       <c r="F1461">
         <v>60</v>
@@ -64171,13 +64164,13 @@
     </row>
     <row r="1462" spans="1:10">
       <c r="A1462" t="s">
-        <v>5622</v>
+        <v>5620</v>
       </c>
       <c r="B1462" s="9" t="s">
-        <v>5623</v>
+        <v>5621</v>
       </c>
       <c r="C1462" t="s">
-        <v>5631</v>
+        <v>5629</v>
       </c>
       <c r="D1462" t="s">
         <v>4052</v>

--- a/themes.xlsx
+++ b/themes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YUMIN\Desktop\B0KT2A_RSVN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF8984E-3D0D-4833-B058-7689B91145C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8993FA25-7756-4782-A653-153C16A919D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63C5B486-270E-41C5-B25C-D463C559813C}"/>
   </bookViews>
   <sheets>
     <sheet name="themes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11745" uniqueCount="5687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11753" uniqueCount="5691">
   <si>
     <t>store_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -21149,9 +21149,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1050,1200,1310,1420,1530,1640,1750,1900,2010,2120</t>
-  </si>
-  <si>
     <t>0950,1120,1250,1420,1550,1720,1850,2020,2150</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -21387,6 +21384,24 @@
   </si>
   <si>
     <t>TURN,턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zw_kd2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오르골</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100,1210,1320,1430,1540,1650,1800,1910,2020,2130</t>
+  </si>
+  <si>
+    <t>1040,1150,1300,1410,1520,1630,1740,1850,2000,2110</t>
+  </si>
+  <si>
+    <t>1145,1310,1435,1600,1725,1850,2015,2140,2305</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -21888,7 +21903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6A8B62-C038-47D4-9D17-9A5AC9BFE2AE}">
-  <dimension ref="A1:L1472"/>
+  <dimension ref="A1:L1473"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
@@ -28187,7 +28202,7 @@
         <v>338</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>5625</v>
+        <v>5624</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>816</v>
@@ -28378,10 +28393,10 @@
         <v>659</v>
       </c>
       <c r="D224" t="s">
+        <v>5646</v>
+      </c>
+      <c r="E224" t="s">
         <v>5647</v>
-      </c>
-      <c r="E224" t="s">
-        <v>5648</v>
       </c>
       <c r="F224">
         <v>70</v>
@@ -28390,7 +28405,7 @@
         <v>335</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>5649</v>
+        <v>5648</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>664</v>
@@ -28462,25 +28477,25 @@
         <v>658</v>
       </c>
       <c r="C227" t="s">
+        <v>5650</v>
+      </c>
+      <c r="D227" t="s">
         <v>5651</v>
       </c>
-      <c r="D227" t="s">
-        <v>5652</v>
-      </c>
       <c r="E227" t="s">
-        <v>5654</v>
+        <v>5653</v>
       </c>
       <c r="F227">
         <v>30</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>5653</v>
+        <v>5652</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>5650</v>
+        <v>5649</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>5650</v>
+        <v>5649</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -30092,7 +30107,7 @@
         <v>336</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>5643</v>
+        <v>5642</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>136</v>
@@ -37154,7 +37169,7 @@
         <v>332</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>5624</v>
+        <v>5623</v>
       </c>
       <c r="J526" s="1" t="s">
         <v>2516</v>
@@ -37186,7 +37201,7 @@
         <v>2817</v>
       </c>
       <c r="J527" s="1" t="s">
-        <v>5623</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="528" spans="1:10">
@@ -40562,13 +40577,13 @@
         <v>1435</v>
       </c>
       <c r="C643" t="s">
-        <v>5646</v>
+        <v>5645</v>
       </c>
       <c r="D643" t="s">
-        <v>5645</v>
+        <v>5644</v>
       </c>
       <c r="E643" t="s">
-        <v>5645</v>
+        <v>5644</v>
       </c>
       <c r="F643">
         <v>70</v>
@@ -40577,7 +40592,7 @@
         <v>337</v>
       </c>
       <c r="H643" s="1" t="s">
-        <v>5644</v>
+        <v>5643</v>
       </c>
       <c r="J643" s="1" t="s">
         <v>1492</v>
@@ -51890,10 +51905,10 @@
         <v>561</v>
       </c>
       <c r="D1033" t="s">
-        <v>5655</v>
+        <v>5654</v>
       </c>
       <c r="E1033" t="s">
-        <v>5679</v>
+        <v>5678</v>
       </c>
       <c r="F1033">
         <v>70</v>
@@ -51905,7 +51920,7 @@
         <v>1428</v>
       </c>
       <c r="J1033" s="1" t="s">
-        <v>5656</v>
+        <v>5655</v>
       </c>
     </row>
     <row r="1034" spans="1:10">
@@ -57986,13 +58001,13 @@
         <v>41</v>
       </c>
       <c r="C1243" t="s">
+        <v>5679</v>
+      </c>
+      <c r="D1243" t="s">
         <v>5680</v>
       </c>
-      <c r="D1243" t="s">
+      <c r="E1243" t="s">
         <v>5681</v>
-      </c>
-      <c r="E1243" t="s">
-        <v>5682</v>
       </c>
       <c r="F1243">
         <v>90</v>
@@ -58001,10 +58016,10 @@
         <v>332</v>
       </c>
       <c r="H1243" s="1" t="s">
-        <v>5683</v>
+        <v>5682</v>
       </c>
       <c r="J1243" s="1" t="s">
-        <v>5683</v>
+        <v>5682</v>
       </c>
     </row>
     <row r="1244" spans="1:11">
@@ -62099,13 +62114,13 @@
         <v>3065</v>
       </c>
       <c r="C1384" t="s">
+        <v>5625</v>
+      </c>
+      <c r="D1384" t="s">
         <v>5626</v>
       </c>
-      <c r="D1384" t="s">
-        <v>5627</v>
-      </c>
       <c r="E1384" t="s">
-        <v>5627</v>
+        <v>5626</v>
       </c>
       <c r="F1384">
         <v>75</v>
@@ -64205,10 +64220,10 @@
         <v>3989</v>
       </c>
       <c r="H1456" s="1" t="s">
+        <v>5627</v>
+      </c>
+      <c r="J1456" s="1" t="s">
         <v>5628</v>
-      </c>
-      <c r="J1456" s="1" t="s">
-        <v>5629</v>
       </c>
     </row>
     <row r="1457" spans="1:10">
@@ -64309,56 +64324,56 @@
         <v>332</v>
       </c>
       <c r="H1460" s="1" t="s">
-        <v>5622</v>
+        <v>5689</v>
       </c>
       <c r="J1460" s="1" t="s">
-        <v>5622</v>
+        <v>5689</v>
       </c>
     </row>
     <row r="1461" spans="1:10">
       <c r="A1461" s="8" t="s">
-        <v>5630</v>
+        <v>5617</v>
       </c>
       <c r="B1461" s="9" t="s">
-        <v>5631</v>
+        <v>5618</v>
       </c>
       <c r="C1461" s="8" t="s">
-        <v>5632</v>
+        <v>5686</v>
       </c>
       <c r="D1461" t="s">
-        <v>5633</v>
+        <v>5687</v>
       </c>
       <c r="E1461" t="s">
-        <v>5633</v>
+        <v>5687</v>
       </c>
       <c r="F1461">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G1461" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H1461" s="1" t="s">
-        <v>1691</v>
+        <v>5688</v>
       </c>
       <c r="J1461" s="1" t="s">
-        <v>1691</v>
+        <v>5688</v>
       </c>
     </row>
     <row r="1462" spans="1:10">
       <c r="A1462" s="8" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B1462" s="9" t="s">
         <v>5630</v>
       </c>
-      <c r="B1462" s="9" t="s">
+      <c r="C1462" s="8" t="s">
         <v>5631</v>
       </c>
-      <c r="C1462" s="8" t="s">
-        <v>5634</v>
-      </c>
       <c r="D1462" t="s">
-        <v>5637</v>
+        <v>5632</v>
       </c>
       <c r="E1462" t="s">
-        <v>5637</v>
+        <v>5632</v>
       </c>
       <c r="F1462">
         <v>60</v>
@@ -64367,56 +64382,56 @@
         <v>336</v>
       </c>
       <c r="H1462" s="1" t="s">
-        <v>2030</v>
+        <v>1691</v>
       </c>
       <c r="J1462" s="1" t="s">
-        <v>2030</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1463" spans="1:10">
       <c r="A1463" s="8" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B1463" s="9" t="s">
         <v>5630</v>
       </c>
-      <c r="B1463" s="9" t="s">
-        <v>5631</v>
-      </c>
       <c r="C1463" s="8" t="s">
-        <v>5635</v>
+        <v>5633</v>
       </c>
       <c r="D1463" t="s">
-        <v>5638</v>
+        <v>5636</v>
       </c>
       <c r="E1463" t="s">
-        <v>5639</v>
+        <v>5636</v>
       </c>
       <c r="F1463">
         <v>60</v>
       </c>
       <c r="G1463" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1463" s="1" t="s">
-        <v>5640</v>
+        <v>2030</v>
       </c>
       <c r="J1463" s="1" t="s">
-        <v>5640</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1464" spans="1:10">
       <c r="A1464" s="8" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B1464" s="9" t="s">
         <v>5630</v>
       </c>
-      <c r="B1464" s="9" t="s">
-        <v>5631</v>
-      </c>
       <c r="C1464" s="8" t="s">
-        <v>5636</v>
+        <v>5634</v>
       </c>
       <c r="D1464" t="s">
-        <v>5641</v>
+        <v>5637</v>
       </c>
       <c r="E1464" t="s">
-        <v>5641</v>
+        <v>5638</v>
       </c>
       <c r="F1464">
         <v>60</v>
@@ -64425,27 +64440,27 @@
         <v>337</v>
       </c>
       <c r="H1464" s="1" t="s">
-        <v>5642</v>
+        <v>5639</v>
       </c>
       <c r="J1464" s="1" t="s">
-        <v>5642</v>
+        <v>5639</v>
       </c>
     </row>
     <row r="1465" spans="1:10">
       <c r="A1465" s="8" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B1465" s="9" t="s">
         <v>5630</v>
       </c>
-      <c r="B1465" s="9" t="s">
-        <v>5631</v>
-      </c>
       <c r="C1465" s="8" t="s">
-        <v>5684</v>
+        <v>5635</v>
       </c>
       <c r="D1465" t="s">
-        <v>5685</v>
+        <v>5640</v>
       </c>
       <c r="E1465" t="s">
-        <v>5686</v>
+        <v>5640</v>
       </c>
       <c r="F1465">
         <v>60</v>
@@ -64454,147 +64469,176 @@
         <v>337</v>
       </c>
       <c r="H1465" s="1" t="s">
+        <v>5641</v>
+      </c>
+      <c r="J1465" s="1" t="s">
+        <v>5641</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:10">
+      <c r="A1466" s="8" t="s">
+        <v>5629</v>
+      </c>
+      <c r="B1466" s="9" t="s">
+        <v>5630</v>
+      </c>
+      <c r="C1466" s="8" t="s">
+        <v>5683</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>5684</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>5685</v>
+      </c>
+      <c r="F1466">
+        <v>60</v>
+      </c>
+      <c r="G1466" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1466" s="1" t="s">
         <v>2082</v>
       </c>
-      <c r="J1465" s="1" t="s">
+      <c r="J1466" s="1" t="s">
         <v>2082</v>
-      </c>
-    </row>
-    <row r="1466" spans="1:10">
-      <c r="A1466" t="s">
-        <v>5660</v>
-      </c>
-      <c r="B1466" t="s">
-        <v>5659</v>
-      </c>
-      <c r="C1466" t="s">
-        <v>5661</v>
-      </c>
-      <c r="D1466" t="s">
-        <v>5657</v>
-      </c>
-      <c r="E1466" t="s">
-        <v>5658</v>
-      </c>
-      <c r="F1466">
-        <v>75</v>
-      </c>
-      <c r="G1466" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H1466" s="1" t="s">
-        <v>2466</v>
-      </c>
-      <c r="J1466" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="1467" spans="1:10">
       <c r="A1467" t="s">
-        <v>5662</v>
-      </c>
-      <c r="B1467" s="9" t="s">
-        <v>5663</v>
+        <v>5659</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>5658</v>
       </c>
       <c r="C1467" t="s">
-        <v>5664</v>
+        <v>5660</v>
       </c>
       <c r="D1467" t="s">
-        <v>5665</v>
+        <v>5656</v>
       </c>
       <c r="E1467" t="s">
-        <v>5665</v>
+        <v>5657</v>
       </c>
       <c r="F1467">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G1467" s="3" t="s">
         <v>334</v>
       </c>
+      <c r="H1467" s="1" t="s">
+        <v>5690</v>
+      </c>
+      <c r="J1467" s="1" t="s">
+        <v>3242</v>
+      </c>
     </row>
     <row r="1468" spans="1:10">
       <c r="A1468" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1468" s="9" t="s">
         <v>5662</v>
       </c>
-      <c r="B1468" s="9" t="s">
+      <c r="C1468" t="s">
         <v>5663</v>
       </c>
-      <c r="C1468" t="s">
-        <v>5666</v>
-      </c>
       <c r="D1468" t="s">
-        <v>5671</v>
+        <v>5664</v>
       </c>
       <c r="E1468" t="s">
-        <v>5676</v>
+        <v>5664</v>
+      </c>
+      <c r="F1468">
+        <v>75</v>
+      </c>
+      <c r="G1468" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="1469" spans="1:10">
       <c r="A1469" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1469" s="9" t="s">
         <v>5662</v>
       </c>
-      <c r="B1469" s="9" t="s">
-        <v>5663</v>
-      </c>
       <c r="C1469" t="s">
-        <v>5667</v>
+        <v>5665</v>
       </c>
       <c r="D1469" t="s">
-        <v>5672</v>
+        <v>5670</v>
       </c>
       <c r="E1469" t="s">
-        <v>5677</v>
+        <v>5675</v>
       </c>
     </row>
     <row r="1470" spans="1:10">
       <c r="A1470" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1470" s="9" t="s">
         <v>5662</v>
       </c>
-      <c r="B1470" s="9" t="s">
-        <v>5663</v>
-      </c>
       <c r="C1470" t="s">
-        <v>5668</v>
+        <v>5666</v>
       </c>
       <c r="D1470" t="s">
-        <v>5673</v>
+        <v>5671</v>
       </c>
       <c r="E1470" t="s">
-        <v>5673</v>
+        <v>5676</v>
       </c>
     </row>
     <row r="1471" spans="1:10">
       <c r="A1471" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1471" s="9" t="s">
         <v>5662</v>
       </c>
-      <c r="B1471" s="9" t="s">
-        <v>5663</v>
-      </c>
       <c r="C1471" t="s">
-        <v>5669</v>
+        <v>5667</v>
       </c>
       <c r="D1471" t="s">
-        <v>5674</v>
+        <v>5672</v>
       </c>
       <c r="E1471" t="s">
-        <v>5678</v>
+        <v>5672</v>
       </c>
     </row>
     <row r="1472" spans="1:10">
       <c r="A1472" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1472" s="9" t="s">
         <v>5662</v>
       </c>
-      <c r="B1472" s="9" t="s">
-        <v>5663</v>
-      </c>
       <c r="C1472" t="s">
-        <v>5670</v>
+        <v>5668</v>
       </c>
       <c r="D1472" t="s">
-        <v>5675</v>
+        <v>5673</v>
       </c>
       <c r="E1472" t="s">
-        <v>5675</v>
+        <v>5677</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:5">
+      <c r="A1473" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1473" s="9" t="s">
+        <v>5662</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>5669</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>5674</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>5674</v>
       </c>
     </row>
   </sheetData>
